--- a/output/tables/rolling_dy_results.xlsx
+++ b/output/tables/rolling_dy_results.xlsx
@@ -459,10 +459,10 @@
         <v>43252</v>
       </c>
       <c r="B2" t="n">
-        <v>44.84198208575464</v>
+        <v>44.84315957057574</v>
       </c>
       <c r="C2" t="n">
-        <v>3.985827893935175</v>
+        <v>3.986221890980217</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -473,10 +473,10 @@
         <v>43259</v>
       </c>
       <c r="B3" t="n">
-        <v>46.40028493598334</v>
+        <v>46.40126375194029</v>
       </c>
       <c r="C3" t="n">
-        <v>4.744383937900523</v>
+        <v>4.744666379627462</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
@@ -487,10 +487,10 @@
         <v>43266</v>
       </c>
       <c r="B4" t="n">
-        <v>46.38751177756831</v>
+        <v>46.38834146395442</v>
       </c>
       <c r="C4" t="n">
-        <v>4.678769227759849</v>
+        <v>4.67906307515999</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
@@ -501,10 +501,10 @@
         <v>43273</v>
       </c>
       <c r="B5" t="n">
-        <v>48.11171251996856</v>
+        <v>48.1128209135578</v>
       </c>
       <c r="C5" t="n">
-        <v>5.126834466287862</v>
+        <v>5.127269564533115</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
@@ -515,10 +515,10 @@
         <v>43280</v>
       </c>
       <c r="B6" t="n">
-        <v>49.12268111090889</v>
+        <v>49.12400013413724</v>
       </c>
       <c r="C6" t="n">
-        <v>2.902567199864135</v>
+        <v>2.90262931339742</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
@@ -529,10 +529,10 @@
         <v>43287</v>
       </c>
       <c r="B7" t="n">
-        <v>48.67570984169087</v>
+        <v>48.67701271308596</v>
       </c>
       <c r="C7" t="n">
-        <v>2.639711813223568</v>
+        <v>2.639640166155562</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
@@ -543,10 +543,10 @@
         <v>43294</v>
       </c>
       <c r="B8" t="n">
-        <v>48.50136605661717</v>
+        <v>48.50243783026335</v>
       </c>
       <c r="C8" t="n">
-        <v>2.808516423920519</v>
+        <v>2.808456502430647</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
@@ -557,10 +557,10 @@
         <v>43301</v>
       </c>
       <c r="B9" t="n">
-        <v>49.18331558945763</v>
+        <v>49.1843521749347</v>
       </c>
       <c r="C9" t="n">
-        <v>2.826945209064186</v>
+        <v>2.826949126302219</v>
       </c>
       <c r="D9" t="n">
         <v>1</v>
@@ -571,10 +571,10 @@
         <v>43308</v>
       </c>
       <c r="B10" t="n">
-        <v>49.58260218950267</v>
+        <v>49.58362063709027</v>
       </c>
       <c r="C10" t="n">
-        <v>4.664100482658901</v>
+        <v>4.664011486568887</v>
       </c>
       <c r="D10" t="n">
         <v>1</v>
@@ -585,10 +585,10 @@
         <v>43315</v>
       </c>
       <c r="B11" t="n">
-        <v>49.83872150137693</v>
+        <v>49.84000145842018</v>
       </c>
       <c r="C11" t="n">
-        <v>4.517671910193064</v>
+        <v>4.517575222311824</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
@@ -599,10 +599,10 @@
         <v>43322</v>
       </c>
       <c r="B12" t="n">
-        <v>48.46778591507609</v>
+        <v>48.46929366212029</v>
       </c>
       <c r="C12" t="n">
-        <v>2.952632578662319</v>
+        <v>2.952558078948934</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
@@ -613,10 +613,10 @@
         <v>43329</v>
       </c>
       <c r="B13" t="n">
-        <v>47.8741932016272</v>
+        <v>47.87576355435334</v>
       </c>
       <c r="C13" t="n">
-        <v>2.920677671118977</v>
+        <v>2.920588576441693</v>
       </c>
       <c r="D13" t="n">
         <v>1</v>
@@ -627,10 +627,10 @@
         <v>43336</v>
       </c>
       <c r="B14" t="n">
-        <v>47.51031095138325</v>
+        <v>47.51196291125027</v>
       </c>
       <c r="C14" t="n">
-        <v>2.826596816394145</v>
+        <v>2.826506661005751</v>
       </c>
       <c r="D14" t="n">
         <v>1</v>
@@ -641,10 +641,10 @@
         <v>43343</v>
       </c>
       <c r="B15" t="n">
-        <v>47.53446284831944</v>
+        <v>47.5361978544625</v>
       </c>
       <c r="C15" t="n">
-        <v>3.025897359874866</v>
+        <v>3.025865863701899</v>
       </c>
       <c r="D15" t="n">
         <v>1</v>
@@ -655,10 +655,10 @@
         <v>43350</v>
       </c>
       <c r="B16" t="n">
-        <v>47.64664016960042</v>
+        <v>47.6481998386889</v>
       </c>
       <c r="C16" t="n">
-        <v>3.378027838633858</v>
+        <v>3.37791678656523</v>
       </c>
       <c r="D16" t="n">
         <v>1</v>
@@ -669,10 +669,10 @@
         <v>43357</v>
       </c>
       <c r="B17" t="n">
-        <v>47.6605251939454</v>
+        <v>47.66216188163704</v>
       </c>
       <c r="C17" t="n">
-        <v>3.419891863976425</v>
+        <v>3.419765476255097</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -683,10 +683,10 @@
         <v>43364</v>
       </c>
       <c r="B18" t="n">
-        <v>49.04669820609672</v>
+        <v>49.04817837734666</v>
       </c>
       <c r="C18" t="n">
-        <v>3.437721571975271</v>
+        <v>3.437575508000141</v>
       </c>
       <c r="D18" t="n">
         <v>1</v>
@@ -697,10 +697,10 @@
         <v>43371</v>
       </c>
       <c r="B19" t="n">
-        <v>49.00219835224271</v>
+        <v>49.00355726333346</v>
       </c>
       <c r="C19" t="n">
-        <v>3.185595227240348</v>
+        <v>3.185401392021154</v>
       </c>
       <c r="D19" t="n">
         <v>1</v>
@@ -711,10 +711,10 @@
         <v>43378</v>
       </c>
       <c r="B20" t="n">
-        <v>49.14449131555341</v>
+        <v>49.14578694297174</v>
       </c>
       <c r="C20" t="n">
-        <v>3.038242621343122</v>
+        <v>3.038091199169494</v>
       </c>
       <c r="D20" t="n">
         <v>1</v>
@@ -725,10 +725,10 @@
         <v>43385</v>
       </c>
       <c r="B21" t="n">
-        <v>49.73106298468809</v>
+        <v>49.73248182801047</v>
       </c>
       <c r="C21" t="n">
-        <v>3.042109290944078</v>
+        <v>3.041895797482496</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -739,10 +739,10 @@
         <v>43392</v>
       </c>
       <c r="B22" t="n">
-        <v>49.97115041617238</v>
+        <v>49.97271665441794</v>
       </c>
       <c r="C22" t="n">
-        <v>3.091940885258273</v>
+        <v>3.091773744480961</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
@@ -753,10 +753,10 @@
         <v>43399</v>
       </c>
       <c r="B23" t="n">
-        <v>50.98921210821353</v>
+        <v>50.99039193233659</v>
       </c>
       <c r="C23" t="n">
-        <v>2.971989495343466</v>
+        <v>2.971792144435233</v>
       </c>
       <c r="D23" t="n">
         <v>1</v>
@@ -767,10 +767,10 @@
         <v>43406</v>
       </c>
       <c r="B24" t="n">
-        <v>51.18504693026748</v>
+        <v>51.18584301047866</v>
       </c>
       <c r="C24" t="n">
-        <v>2.75980885581032</v>
+        <v>2.759677970589224</v>
       </c>
       <c r="D24" t="n">
         <v>1</v>
@@ -781,10 +781,10 @@
         <v>43413</v>
       </c>
       <c r="B25" t="n">
-        <v>50.5197354499914</v>
+        <v>50.52056018949535</v>
       </c>
       <c r="C25" t="n">
-        <v>2.708551291023552</v>
+        <v>2.708458908459386</v>
       </c>
       <c r="D25" t="n">
         <v>1</v>
@@ -795,10 +795,10 @@
         <v>43420</v>
       </c>
       <c r="B26" t="n">
-        <v>50.82484594494136</v>
+        <v>50.82587297429284</v>
       </c>
       <c r="C26" t="n">
-        <v>2.334948441146299</v>
+        <v>2.334939258995822</v>
       </c>
       <c r="D26" t="n">
         <v>1</v>
@@ -809,10 +809,10 @@
         <v>43427</v>
       </c>
       <c r="B27" t="n">
-        <v>52.47542739802656</v>
+        <v>52.47763781740238</v>
       </c>
       <c r="C27" t="n">
-        <v>1.852591593091238</v>
+        <v>1.852678897551119</v>
       </c>
       <c r="D27" t="n">
         <v>1</v>
@@ -823,10 +823,10 @@
         <v>43434</v>
       </c>
       <c r="B28" t="n">
-        <v>52.76761398934919</v>
+        <v>52.76988650030548</v>
       </c>
       <c r="C28" t="n">
-        <v>2.279930416526935</v>
+        <v>2.280135033560481</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>43441</v>
       </c>
       <c r="B29" t="n">
-        <v>52.69456458276614</v>
+        <v>52.69686861612468</v>
       </c>
       <c r="C29" t="n">
-        <v>1.893116723171693</v>
+        <v>1.893322807877776</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -851,10 +851,10 @@
         <v>43448</v>
       </c>
       <c r="B30" t="n">
-        <v>53.19337190297586</v>
+        <v>53.19575387948345</v>
       </c>
       <c r="C30" t="n">
-        <v>1.905127881883659</v>
+        <v>1.905314311066833</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -865,10 +865,10 @@
         <v>43455</v>
       </c>
       <c r="B31" t="n">
-        <v>52.22837842951492</v>
+        <v>52.23073721784242</v>
       </c>
       <c r="C31" t="n">
-        <v>1.985790096378462</v>
+        <v>1.985889775025313</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
@@ -879,10 +879,10 @@
         <v>43462</v>
       </c>
       <c r="B32" t="n">
-        <v>52.17130195475406</v>
+        <v>52.17347245647996</v>
       </c>
       <c r="C32" t="n">
-        <v>2.105677158550521</v>
+        <v>2.105804179216208</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
@@ -893,10 +893,10 @@
         <v>43469</v>
       </c>
       <c r="B33" t="n">
-        <v>52.59651191524774</v>
+        <v>52.59869113986448</v>
       </c>
       <c r="C33" t="n">
-        <v>2.021953539038757</v>
+        <v>2.022037973438563</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -907,10 +907,10 @@
         <v>43476</v>
       </c>
       <c r="B34" t="n">
-        <v>52.04633860818177</v>
+        <v>52.04850071535011</v>
       </c>
       <c r="C34" t="n">
-        <v>2.011128814807175</v>
+        <v>2.01118523203759</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
@@ -921,10 +921,10 @@
         <v>43483</v>
       </c>
       <c r="B35" t="n">
-        <v>51.65156488312437</v>
+        <v>51.65390179691081</v>
       </c>
       <c r="C35" t="n">
-        <v>1.790187130864634</v>
+        <v>1.790275481183288</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -935,10 +935,10 @@
         <v>43490</v>
       </c>
       <c r="B36" t="n">
-        <v>51.23870751594981</v>
+        <v>51.24095663358884</v>
       </c>
       <c r="C36" t="n">
-        <v>1.661101671681101</v>
+        <v>1.661213590693277</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -949,10 +949,10 @@
         <v>43497</v>
       </c>
       <c r="B37" t="n">
-        <v>51.5571016267785</v>
+        <v>51.55915707098473</v>
       </c>
       <c r="C37" t="n">
-        <v>1.969545326730094</v>
+        <v>1.969601624620469</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -963,10 +963,10 @@
         <v>43504</v>
       </c>
       <c r="B38" t="n">
-        <v>51.16588050940315</v>
+        <v>51.167993954096</v>
       </c>
       <c r="C38" t="n">
-        <v>2.222392206093679</v>
+        <v>2.222423812155843</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
@@ -977,10 +977,10 @@
         <v>43511</v>
       </c>
       <c r="B39" t="n">
-        <v>51.69026579216249</v>
+        <v>51.69197238659404</v>
       </c>
       <c r="C39" t="n">
-        <v>2.31936442838686</v>
+        <v>2.319426801997695</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -991,10 +991,10 @@
         <v>43518</v>
       </c>
       <c r="B40" t="n">
-        <v>51.27074808515622</v>
+        <v>51.27240973589232</v>
       </c>
       <c r="C40" t="n">
-        <v>2.417635778695389</v>
+        <v>2.417668855501161</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
@@ -1005,10 +1005,10 @@
         <v>43525</v>
       </c>
       <c r="B41" t="n">
-        <v>51.41144373944729</v>
+        <v>51.41301782133573</v>
       </c>
       <c r="C41" t="n">
-        <v>2.506563445322518</v>
+        <v>2.506461035563368</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -1019,10 +1019,10 @@
         <v>43532</v>
       </c>
       <c r="B42" t="n">
-        <v>51.39174105439107</v>
+        <v>51.39319157636631</v>
       </c>
       <c r="C42" t="n">
-        <v>2.6164153371476</v>
+        <v>2.616229630233322</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
@@ -1033,10 +1033,10 @@
         <v>43539</v>
       </c>
       <c r="B43" t="n">
-        <v>50.81599808202157</v>
+        <v>50.81742569213397</v>
       </c>
       <c r="C43" t="n">
-        <v>2.028856030029607</v>
+        <v>2.028712557532455</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
@@ -1047,10 +1047,10 @@
         <v>43546</v>
       </c>
       <c r="B44" t="n">
-        <v>50.95313525396446</v>
+        <v>50.95452666315031</v>
       </c>
       <c r="C44" t="n">
-        <v>2.185044730499277</v>
+        <v>2.18486179038703</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>43553</v>
       </c>
       <c r="B45" t="n">
-        <v>49.41950986835</v>
+        <v>49.42015944652024</v>
       </c>
       <c r="C45" t="n">
-        <v>2.604151942614028</v>
+        <v>2.60407963539777</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -1075,10 +1075,10 @@
         <v>43560</v>
       </c>
       <c r="B46" t="n">
-        <v>48.96243507005142</v>
+        <v>48.96316653876704</v>
       </c>
       <c r="C46" t="n">
-        <v>2.58525229673887</v>
+        <v>2.585086962763341</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
@@ -1089,10 +1089,10 @@
         <v>43567</v>
       </c>
       <c r="B47" t="n">
-        <v>47.90337513956089</v>
+        <v>47.90377807176763</v>
       </c>
       <c r="C47" t="n">
-        <v>3.756813580467374</v>
+        <v>3.756794459260349</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -1103,10 +1103,10 @@
         <v>43574</v>
       </c>
       <c r="B48" t="n">
-        <v>48.31571029149246</v>
+        <v>48.31612090186235</v>
       </c>
       <c r="C48" t="n">
-        <v>2.797825952729332</v>
+        <v>2.797771847930433</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -1117,10 +1117,10 @@
         <v>43581</v>
       </c>
       <c r="B49" t="n">
-        <v>48.53545505420278</v>
+        <v>48.53573524095768</v>
       </c>
       <c r="C49" t="n">
-        <v>2.885741976987765</v>
+        <v>2.885638569015361</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -1131,10 +1131,10 @@
         <v>43588</v>
       </c>
       <c r="B50" t="n">
-        <v>49.01157016731386</v>
+        <v>49.01186260135434</v>
       </c>
       <c r="C50" t="n">
-        <v>2.870463557908238</v>
+        <v>2.870345587566042</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -1145,10 +1145,10 @@
         <v>43595</v>
       </c>
       <c r="B51" t="n">
-        <v>49.19530717683001</v>
+        <v>49.19560507902005</v>
       </c>
       <c r="C51" t="n">
-        <v>2.649405792856101</v>
+        <v>2.649319155599268</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
@@ -1159,10 +1159,10 @@
         <v>43602</v>
       </c>
       <c r="B52" t="n">
-        <v>49.27768555552748</v>
+        <v>49.27809618036965</v>
       </c>
       <c r="C52" t="n">
-        <v>2.573514132006467</v>
+        <v>2.57341893505937</v>
       </c>
       <c r="D52" t="n">
         <v>0</v>
@@ -1173,10 +1173,10 @@
         <v>43609</v>
       </c>
       <c r="B53" t="n">
-        <v>48.82733931483665</v>
+        <v>48.82774020711998</v>
       </c>
       <c r="C53" t="n">
-        <v>2.807926724341417</v>
+        <v>2.807899716739252</v>
       </c>
       <c r="D53" t="n">
         <v>0</v>
@@ -1187,10 +1187,10 @@
         <v>43616</v>
       </c>
       <c r="B54" t="n">
-        <v>46.36315527193997</v>
+        <v>46.36359010919455</v>
       </c>
       <c r="C54" t="n">
-        <v>1.510925690110179</v>
+        <v>1.510909769142406</v>
       </c>
       <c r="D54" t="n">
         <v>0</v>
@@ -1201,10 +1201,10 @@
         <v>43623</v>
       </c>
       <c r="B55" t="n">
-        <v>47.56230747352109</v>
+        <v>47.5627774527612</v>
       </c>
       <c r="C55" t="n">
-        <v>2.131982208832142</v>
+        <v>2.131978610610668</v>
       </c>
       <c r="D55" t="n">
         <v>0</v>
@@ -1215,10 +1215,10 @@
         <v>43630</v>
       </c>
       <c r="B56" t="n">
-        <v>46.74664687359333</v>
+        <v>46.74677326071525</v>
       </c>
       <c r="C56" t="n">
-        <v>2.332033463097946</v>
+        <v>2.332202255608442</v>
       </c>
       <c r="D56" t="n">
         <v>0</v>
@@ -1229,10 +1229,10 @@
         <v>43637</v>
       </c>
       <c r="B57" t="n">
-        <v>46.94839614551416</v>
+        <v>46.94867720170225</v>
       </c>
       <c r="C57" t="n">
-        <v>2.203334630763697</v>
+        <v>2.203372946403635</v>
       </c>
       <c r="D57" t="n">
         <v>0</v>
@@ -1243,10 +1243,10 @@
         <v>43644</v>
       </c>
       <c r="B58" t="n">
-        <v>47.9473873349562</v>
+        <v>47.94816662345397</v>
       </c>
       <c r="C58" t="n">
-        <v>2.467730147800851</v>
+        <v>2.467883317846896</v>
       </c>
       <c r="D58" t="n">
         <v>0</v>
@@ -1257,10 +1257,10 @@
         <v>43651</v>
       </c>
       <c r="B59" t="n">
-        <v>47.64483701168356</v>
+        <v>47.64565271149994</v>
       </c>
       <c r="C59" t="n">
-        <v>2.438909014965552</v>
+        <v>2.439096903022273</v>
       </c>
       <c r="D59" t="n">
         <v>0</v>
@@ -1271,10 +1271,10 @@
         <v>43658</v>
       </c>
       <c r="B60" t="n">
-        <v>56.89583401965862</v>
+        <v>56.89407473858523</v>
       </c>
       <c r="C60" t="n">
-        <v>6.294330904448164</v>
+        <v>6.293355261714325</v>
       </c>
       <c r="D60" t="n">
         <v>0</v>
@@ -1285,10 +1285,10 @@
         <v>43665</v>
       </c>
       <c r="B61" t="n">
-        <v>48.08594929850594</v>
+        <v>48.08667373561917</v>
       </c>
       <c r="C61" t="n">
-        <v>1.868979093150124</v>
+        <v>1.869053620642388</v>
       </c>
       <c r="D61" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>43672</v>
       </c>
       <c r="B62" t="n">
-        <v>48.37158224874329</v>
+        <v>48.37226843860111</v>
       </c>
       <c r="C62" t="n">
-        <v>1.770192657071983</v>
+        <v>1.770222763530228</v>
       </c>
       <c r="D62" t="n">
         <v>0</v>
@@ -1313,10 +1313,10 @@
         <v>43679</v>
       </c>
       <c r="B63" t="n">
-        <v>59.48561515351241</v>
+        <v>59.4844774122864</v>
       </c>
       <c r="C63" t="n">
-        <v>10.89755916267398</v>
+        <v>10.89668124181158</v>
       </c>
       <c r="D63" t="n">
         <v>0</v>
@@ -1327,10 +1327,10 @@
         <v>43686</v>
       </c>
       <c r="B64" t="n">
-        <v>59.41035272091697</v>
+        <v>59.40911319306027</v>
       </c>
       <c r="C64" t="n">
-        <v>11.18543658892428</v>
+        <v>11.18412902354887</v>
       </c>
       <c r="D64" t="n">
         <v>0</v>
@@ -1341,10 +1341,10 @@
         <v>43693</v>
       </c>
       <c r="B65" t="n">
-        <v>49.22925011812716</v>
+        <v>49.22995749042104</v>
       </c>
       <c r="C65" t="n">
-        <v>1.554669570313227</v>
+        <v>1.554708237678517</v>
       </c>
       <c r="D65" t="n">
         <v>0</v>
@@ -1355,10 +1355,10 @@
         <v>43700</v>
       </c>
       <c r="B66" t="n">
-        <v>60.64513476109637</v>
+        <v>60.64432107733947</v>
       </c>
       <c r="C66" t="n">
-        <v>11.95958604620728</v>
+        <v>11.95846189626225</v>
       </c>
       <c r="D66" t="n">
         <v>0</v>
@@ -1369,10 +1369,10 @@
         <v>43707</v>
       </c>
       <c r="B67" t="n">
-        <v>49.45013911428691</v>
+        <v>49.45103278722829</v>
       </c>
       <c r="C67" t="n">
-        <v>1.894649360137024</v>
+        <v>1.894811505306061</v>
       </c>
       <c r="D67" t="n">
         <v>0</v>
@@ -1383,10 +1383,10 @@
         <v>43714</v>
       </c>
       <c r="B68" t="n">
-        <v>49.95924519943755</v>
+        <v>49.960015017643</v>
       </c>
       <c r="C68" t="n">
-        <v>2.000342096573906</v>
+        <v>2.000467441547752</v>
       </c>
       <c r="D68" t="n">
         <v>0</v>
@@ -1397,10 +1397,10 @@
         <v>43721</v>
       </c>
       <c r="B69" t="n">
-        <v>53.2511963027091</v>
+        <v>53.25151805216021</v>
       </c>
       <c r="C69" t="n">
-        <v>2.543894808016231</v>
+        <v>2.544316891010828</v>
       </c>
       <c r="D69" t="n">
         <v>0</v>
@@ -1411,10 +1411,10 @@
         <v>43728</v>
       </c>
       <c r="B70" t="n">
-        <v>64.14420635613133</v>
+        <v>64.14557096573888</v>
       </c>
       <c r="C70" t="n">
-        <v>15.96722987065829</v>
+        <v>15.96809571390129</v>
       </c>
       <c r="D70" t="n">
         <v>0</v>
@@ -1425,10 +1425,10 @@
         <v>43735</v>
       </c>
       <c r="B71" t="n">
-        <v>77.8447118870963</v>
+        <v>77.84653814259562</v>
       </c>
       <c r="C71" t="n">
-        <v>11.69158558745604</v>
+        <v>11.68970211995145</v>
       </c>
       <c r="D71" t="n">
         <v>0</v>
@@ -1439,10 +1439,10 @@
         <v>43742</v>
       </c>
       <c r="B72" t="n">
-        <v>69.67459545192158</v>
+        <v>69.67551873890189</v>
       </c>
       <c r="C72" t="n">
-        <v>13.05297049446187</v>
+        <v>13.05446196748643</v>
       </c>
       <c r="D72" t="n">
         <v>0</v>
@@ -1453,10 +1453,10 @@
         <v>43749</v>
       </c>
       <c r="B73" t="n">
-        <v>69.21399393454357</v>
+        <v>69.21489280956179</v>
       </c>
       <c r="C73" t="n">
-        <v>12.52724882348573</v>
+        <v>12.52844580295941</v>
       </c>
       <c r="D73" t="n">
         <v>0</v>
@@ -1467,10 +1467,10 @@
         <v>43756</v>
       </c>
       <c r="B74" t="n">
-        <v>69.22302533594605</v>
+        <v>69.22390675142361</v>
       </c>
       <c r="C74" t="n">
-        <v>12.25427648165477</v>
+        <v>12.25542392585188</v>
       </c>
       <c r="D74" t="n">
         <v>0</v>
@@ -1481,10 +1481,10 @@
         <v>43763</v>
       </c>
       <c r="B75" t="n">
-        <v>69.47359453117924</v>
+        <v>69.47415988895833</v>
       </c>
       <c r="C75" t="n">
-        <v>12.16675909690342</v>
+        <v>12.16784382956389</v>
       </c>
       <c r="D75" t="n">
         <v>0</v>
@@ -1495,10 +1495,10 @@
         <v>43770</v>
       </c>
       <c r="B76" t="n">
-        <v>68.92019653497535</v>
+        <v>68.92154522779551</v>
       </c>
       <c r="C76" t="n">
-        <v>11.72756692438687</v>
+        <v>11.72936068622941</v>
       </c>
       <c r="D76" t="n">
         <v>0</v>
@@ -1509,10 +1509,10 @@
         <v>43777</v>
       </c>
       <c r="B77" t="n">
-        <v>68.22706529931226</v>
+        <v>68.22800828057957</v>
       </c>
       <c r="C77" t="n">
-        <v>11.91384881373574</v>
+        <v>11.91616983276019</v>
       </c>
       <c r="D77" t="n">
         <v>0</v>
@@ -1523,10 +1523,10 @@
         <v>43784</v>
       </c>
       <c r="B78" t="n">
-        <v>68.96790170673449</v>
+        <v>68.96907654579707</v>
       </c>
       <c r="C78" t="n">
-        <v>13.10618193693914</v>
+        <v>13.10862308393297</v>
       </c>
       <c r="D78" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>43791</v>
       </c>
       <c r="B79" t="n">
-        <v>68.82217955640971</v>
+        <v>68.82319314433128</v>
       </c>
       <c r="C79" t="n">
-        <v>12.81559790030133</v>
+        <v>12.8168340828859</v>
       </c>
       <c r="D79" t="n">
         <v>0</v>
@@ -1551,10 +1551,10 @@
         <v>43798</v>
       </c>
       <c r="B80" t="n">
-        <v>68.9751243873387</v>
+        <v>68.97599356422462</v>
       </c>
       <c r="C80" t="n">
-        <v>13.36396554465704</v>
+        <v>13.36488325955284</v>
       </c>
       <c r="D80" t="n">
         <v>0</v>
@@ -1565,10 +1565,10 @@
         <v>43805</v>
       </c>
       <c r="B81" t="n">
-        <v>69.10711281586282</v>
+        <v>69.10809675824306</v>
       </c>
       <c r="C81" t="n">
-        <v>13.47682237328684</v>
+        <v>13.47800306497723</v>
       </c>
       <c r="D81" t="n">
         <v>0</v>
@@ -1579,10 +1579,10 @@
         <v>43812</v>
       </c>
       <c r="B82" t="n">
-        <v>69.62385248849077</v>
+        <v>69.62493683107692</v>
       </c>
       <c r="C82" t="n">
-        <v>14.39498814335294</v>
+        <v>14.39635526858572</v>
       </c>
       <c r="D82" t="n">
         <v>0</v>
@@ -1593,10 +1593,10 @@
         <v>43819</v>
       </c>
       <c r="B83" t="n">
-        <v>69.35958329094611</v>
+        <v>69.36099335688738</v>
       </c>
       <c r="C83" t="n">
-        <v>13.46208722306476</v>
+        <v>13.46347690928113</v>
       </c>
       <c r="D83" t="n">
         <v>0</v>
@@ -1607,10 +1607,10 @@
         <v>43826</v>
       </c>
       <c r="B84" t="n">
-        <v>68.51407471906982</v>
+        <v>68.51466327143332</v>
       </c>
       <c r="C84" t="n">
-        <v>11.8013491198649</v>
+        <v>11.80175143112641</v>
       </c>
       <c r="D84" t="n">
         <v>0</v>
@@ -1621,10 +1621,10 @@
         <v>43833</v>
       </c>
       <c r="B85" t="n">
-        <v>69.19027511860642</v>
+        <v>69.19079855519119</v>
       </c>
       <c r="C85" t="n">
-        <v>13.89852574685101</v>
+        <v>13.89893475243474</v>
       </c>
       <c r="D85" t="n">
         <v>0</v>
@@ -1635,10 +1635,10 @@
         <v>43840</v>
       </c>
       <c r="B86" t="n">
-        <v>68.44221574413599</v>
+        <v>68.44265731419166</v>
       </c>
       <c r="C86" t="n">
-        <v>12.88970063936654</v>
+        <v>12.89003341263457</v>
       </c>
       <c r="D86" t="n">
         <v>0</v>
@@ -1649,10 +1649,10 @@
         <v>43847</v>
       </c>
       <c r="B87" t="n">
-        <v>68.15880333179722</v>
+        <v>68.15923772760075</v>
       </c>
       <c r="C87" t="n">
-        <v>11.92652538206709</v>
+        <v>11.92681967147805</v>
       </c>
       <c r="D87" t="n">
         <v>0</v>
@@ -1663,10 +1663,10 @@
         <v>43854</v>
       </c>
       <c r="B88" t="n">
-        <v>68.48788383251421</v>
+        <v>68.48821960318776</v>
       </c>
       <c r="C88" t="n">
-        <v>12.25099119161925</v>
+        <v>12.25128201653945</v>
       </c>
       <c r="D88" t="n">
         <v>0</v>
@@ -1677,10 +1677,10 @@
         <v>43861</v>
       </c>
       <c r="B89" t="n">
-        <v>70.35068190585336</v>
+        <v>70.35078436963494</v>
       </c>
       <c r="C89" t="n">
-        <v>12.81435304710331</v>
+        <v>12.81453757970699</v>
       </c>
       <c r="D89" t="n">
         <v>0</v>
@@ -1691,10 +1691,10 @@
         <v>43868</v>
       </c>
       <c r="B90" t="n">
-        <v>68.3692749948703</v>
+        <v>68.36970151886803</v>
       </c>
       <c r="C90" t="n">
-        <v>12.54077769611153</v>
+        <v>12.54081949627769</v>
       </c>
       <c r="D90" t="n">
         <v>0</v>
@@ -1705,10 +1705,10 @@
         <v>43875</v>
       </c>
       <c r="B91" t="n">
-        <v>73.29432250132464</v>
+        <v>73.29389506823033</v>
       </c>
       <c r="C91" t="n">
-        <v>16.6276075278356</v>
+        <v>16.62548964605035</v>
       </c>
       <c r="D91" t="n">
         <v>0</v>
@@ -1719,10 +1719,10 @@
         <v>43882</v>
       </c>
       <c r="B92" t="n">
-        <v>73.6189925171707</v>
+        <v>73.61845754359986</v>
       </c>
       <c r="C92" t="n">
-        <v>16.83012554899642</v>
+        <v>16.82812303639445</v>
       </c>
       <c r="D92" t="n">
         <v>0</v>
@@ -1733,10 +1733,10 @@
         <v>43889</v>
       </c>
       <c r="B93" t="n">
-        <v>69.83013710663926</v>
+        <v>69.83031853928969</v>
       </c>
       <c r="C93" t="n">
-        <v>11.87817696245312</v>
+        <v>11.87829659368497</v>
       </c>
       <c r="D93" t="n">
         <v>0</v>
@@ -1747,10 +1747,10 @@
         <v>43896</v>
       </c>
       <c r="B94" t="n">
-        <v>68.10903416795658</v>
+        <v>68.10925119391379</v>
       </c>
       <c r="C94" t="n">
-        <v>11.79834751506518</v>
+        <v>11.79816570000021</v>
       </c>
       <c r="D94" t="n">
         <v>0</v>
@@ -1761,10 +1761,10 @@
         <v>43903</v>
       </c>
       <c r="B95" t="n">
-        <v>68.63926532912255</v>
+        <v>68.63943489696747</v>
       </c>
       <c r="C95" t="n">
-        <v>12.07296392806935</v>
+        <v>12.07266273210165</v>
       </c>
       <c r="D95" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>43910</v>
       </c>
       <c r="B96" t="n">
-        <v>69.3249141529741</v>
+        <v>69.32509194835872</v>
       </c>
       <c r="C96" t="n">
-        <v>11.47892757032809</v>
+        <v>11.4787764913048</v>
       </c>
       <c r="D96" t="n">
         <v>0</v>
@@ -1789,10 +1789,10 @@
         <v>43917</v>
       </c>
       <c r="B97" t="n">
-        <v>70.99591040183986</v>
+        <v>70.99591212539424</v>
       </c>
       <c r="C97" t="n">
-        <v>12.72015335388724</v>
+        <v>12.71962574052241</v>
       </c>
       <c r="D97" t="n">
         <v>0</v>
@@ -1803,10 +1803,10 @@
         <v>43924</v>
       </c>
       <c r="B98" t="n">
-        <v>71.28139949476632</v>
+        <v>71.2817234379883</v>
       </c>
       <c r="C98" t="n">
-        <v>13.51859225749055</v>
+        <v>13.51862452188786</v>
       </c>
       <c r="D98" t="n">
         <v>0</v>
@@ -1817,10 +1817,10 @@
         <v>43931</v>
       </c>
       <c r="B99" t="n">
-        <v>71.65907995822802</v>
+        <v>71.65928871763786</v>
       </c>
       <c r="C99" t="n">
-        <v>14.37604139990868</v>
+        <v>14.3763850734445</v>
       </c>
       <c r="D99" t="n">
         <v>0</v>
@@ -1831,10 +1831,10 @@
         <v>43938</v>
       </c>
       <c r="B100" t="n">
-        <v>71.60229872819038</v>
+        <v>71.60232466446725</v>
       </c>
       <c r="C100" t="n">
-        <v>14.24549411854915</v>
+        <v>14.24545034528859</v>
       </c>
       <c r="D100" t="n">
         <v>0</v>
@@ -1845,10 +1845,10 @@
         <v>43945</v>
       </c>
       <c r="B101" t="n">
-        <v>68.11963281788498</v>
+        <v>68.11976043269628</v>
       </c>
       <c r="C101" t="n">
-        <v>11.22875982949128</v>
+        <v>11.22867136477459</v>
       </c>
       <c r="D101" t="n">
         <v>0</v>
@@ -1859,10 +1859,10 @@
         <v>43952</v>
       </c>
       <c r="B102" t="n">
-        <v>68.0418197372443</v>
+        <v>68.04205576175153</v>
       </c>
       <c r="C102" t="n">
-        <v>11.23733115470684</v>
+        <v>11.23732878802906</v>
       </c>
       <c r="D102" t="n">
         <v>0</v>
@@ -1873,10 +1873,10 @@
         <v>43959</v>
       </c>
       <c r="B103" t="n">
-        <v>70.74108545208935</v>
+        <v>70.74052335752515</v>
       </c>
       <c r="C103" t="n">
-        <v>11.52559036744155</v>
+        <v>11.52460421081675</v>
       </c>
       <c r="D103" t="n">
         <v>0</v>
@@ -1887,10 +1887,10 @@
         <v>43966</v>
       </c>
       <c r="B104" t="n">
-        <v>72.13014243658155</v>
+        <v>72.12954560819769</v>
       </c>
       <c r="C104" t="n">
-        <v>9.964746040830834</v>
+        <v>9.964337921090381</v>
       </c>
       <c r="D104" t="n">
         <v>0</v>
@@ -1901,10 +1901,10 @@
         <v>43973</v>
       </c>
       <c r="B105" t="n">
-        <v>70.71082544542728</v>
+        <v>70.71010038799743</v>
       </c>
       <c r="C105" t="n">
-        <v>10.02014470981918</v>
+        <v>10.01975211031715</v>
       </c>
       <c r="D105" t="n">
         <v>0</v>
@@ -1915,10 +1915,10 @@
         <v>43980</v>
       </c>
       <c r="B106" t="n">
-        <v>67.2630718779992</v>
+        <v>67.26329696369093</v>
       </c>
       <c r="C106" t="n">
-        <v>9.003322849166894</v>
+        <v>9.003350407609421</v>
       </c>
       <c r="D106" t="n">
         <v>0</v>
@@ -1929,10 +1929,10 @@
         <v>43987</v>
       </c>
       <c r="B107" t="n">
-        <v>71.15261576806317</v>
+        <v>71.1518215599496</v>
       </c>
       <c r="C107" t="n">
-        <v>13.13524757010834</v>
+        <v>13.13413777164496</v>
       </c>
       <c r="D107" t="n">
         <v>0</v>
@@ -1943,10 +1943,10 @@
         <v>43994</v>
       </c>
       <c r="B108" t="n">
-        <v>71.62471805366948</v>
+        <v>71.62394875875789</v>
       </c>
       <c r="C108" t="n">
-        <v>16.05560442084675</v>
+        <v>16.05509213361722</v>
       </c>
       <c r="D108" t="n">
         <v>0</v>
@@ -1957,10 +1957,10 @@
         <v>44001</v>
       </c>
       <c r="B109" t="n">
-        <v>74.78708502967042</v>
+        <v>74.7859650122849</v>
       </c>
       <c r="C109" t="n">
-        <v>19.67802453109622</v>
+        <v>19.67719554409219</v>
       </c>
       <c r="D109" t="n">
         <v>0</v>
@@ -1971,10 +1971,10 @@
         <v>44008</v>
       </c>
       <c r="B110" t="n">
-        <v>69.12419677040099</v>
+        <v>69.12417124086784</v>
       </c>
       <c r="C110" t="n">
-        <v>12.87989676742456</v>
+        <v>12.8806559062287</v>
       </c>
       <c r="D110" t="n">
         <v>0</v>
@@ -1985,10 +1985,10 @@
         <v>44015</v>
       </c>
       <c r="B111" t="n">
-        <v>68.9089566909921</v>
+        <v>68.90901934085032</v>
       </c>
       <c r="C111" t="n">
-        <v>12.3848095367467</v>
+        <v>12.38556663998304</v>
       </c>
       <c r="D111" t="n">
         <v>0</v>
@@ -1999,10 +1999,10 @@
         <v>44022</v>
       </c>
       <c r="B112" t="n">
-        <v>68.65116359342205</v>
+        <v>68.65118177808326</v>
       </c>
       <c r="C112" t="n">
-        <v>11.64313788527508</v>
+        <v>11.64393539126166</v>
       </c>
       <c r="D112" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>44029</v>
       </c>
       <c r="B113" t="n">
-        <v>68.11289674194447</v>
+        <v>68.1130634920065</v>
       </c>
       <c r="C113" t="n">
-        <v>10.54117674748288</v>
+        <v>10.54243345992156</v>
       </c>
       <c r="D113" t="n">
         <v>0</v>
@@ -2027,10 +2027,10 @@
         <v>44036</v>
       </c>
       <c r="B114" t="n">
-        <v>68.51871552811527</v>
+        <v>68.51885188681577</v>
       </c>
       <c r="C114" t="n">
-        <v>11.830836602244</v>
+        <v>11.83216039636936</v>
       </c>
       <c r="D114" t="n">
         <v>1</v>
@@ -2041,10 +2041,10 @@
         <v>44043</v>
       </c>
       <c r="B115" t="n">
-        <v>71.87642244618074</v>
+        <v>71.87578620481155</v>
       </c>
       <c r="C115" t="n">
-        <v>18.36300867313554</v>
+        <v>18.36261771608076</v>
       </c>
       <c r="D115" t="n">
         <v>1</v>
@@ -2055,10 +2055,10 @@
         <v>44050</v>
       </c>
       <c r="B116" t="n">
-        <v>69.78541853047558</v>
+        <v>69.78520157764025</v>
       </c>
       <c r="C116" t="n">
-        <v>13.69426081736743</v>
+        <v>13.69476321588817</v>
       </c>
       <c r="D116" t="n">
         <v>1</v>
@@ -2069,10 +2069,10 @@
         <v>44057</v>
       </c>
       <c r="B117" t="n">
-        <v>66.89940279263458</v>
+        <v>66.89965476701417</v>
       </c>
       <c r="C117" t="n">
-        <v>10.70851949548776</v>
+        <v>10.70883641685444</v>
       </c>
       <c r="D117" t="n">
         <v>1</v>
@@ -2083,10 +2083,10 @@
         <v>44064</v>
       </c>
       <c r="B118" t="n">
-        <v>66.21089697085051</v>
+        <v>66.21115743626309</v>
       </c>
       <c r="C118" t="n">
-        <v>10.28888880200495</v>
+        <v>10.28897022751477</v>
       </c>
       <c r="D118" t="n">
         <v>1</v>
@@ -2097,10 +2097,10 @@
         <v>44071</v>
       </c>
       <c r="B119" t="n">
-        <v>60.66828925568795</v>
+        <v>60.66866227000022</v>
       </c>
       <c r="C119" t="n">
-        <v>7.761817252130561</v>
+        <v>7.761570817708931</v>
       </c>
       <c r="D119" t="n">
         <v>1</v>
@@ -2111,10 +2111,10 @@
         <v>44078</v>
       </c>
       <c r="B120" t="n">
-        <v>58.63180451932632</v>
+        <v>58.63235816445948</v>
       </c>
       <c r="C120" t="n">
-        <v>8.250391935865443</v>
+        <v>8.249835935663349</v>
       </c>
       <c r="D120" t="n">
         <v>1</v>
@@ -2125,10 +2125,10 @@
         <v>44085</v>
       </c>
       <c r="B121" t="n">
-        <v>57.80077731521998</v>
+        <v>57.80113453969899</v>
       </c>
       <c r="C121" t="n">
-        <v>7.946084279651247</v>
+        <v>7.945412638735713</v>
       </c>
       <c r="D121" t="n">
         <v>1</v>
@@ -2139,10 +2139,10 @@
         <v>44092</v>
       </c>
       <c r="B122" t="n">
-        <v>45.55761714280393</v>
+        <v>45.55852920825319</v>
       </c>
       <c r="C122" t="n">
-        <v>4.525879402661147</v>
+        <v>4.525607904539819</v>
       </c>
       <c r="D122" t="n">
         <v>1</v>
@@ -2153,10 +2153,10 @@
         <v>44099</v>
       </c>
       <c r="B123" t="n">
-        <v>45.61056255889222</v>
+        <v>45.61157626898211</v>
       </c>
       <c r="C123" t="n">
-        <v>4.771086407160793</v>
+        <v>4.770688711770204</v>
       </c>
       <c r="D123" t="n">
         <v>1</v>
@@ -2167,10 +2167,10 @@
         <v>44106</v>
       </c>
       <c r="B124" t="n">
-        <v>45.83620617157683</v>
+        <v>45.83725847334838</v>
       </c>
       <c r="C124" t="n">
-        <v>4.928696550256793</v>
+        <v>4.92820849212199</v>
       </c>
       <c r="D124" t="n">
         <v>1</v>
@@ -2181,10 +2181,10 @@
         <v>44113</v>
       </c>
       <c r="B125" t="n">
-        <v>45.79687041938789</v>
+        <v>45.79763980463407</v>
       </c>
       <c r="C125" t="n">
-        <v>4.486342804007449</v>
+        <v>4.486044139157696</v>
       </c>
       <c r="D125" t="n">
         <v>1</v>
@@ -2195,10 +2195,10 @@
         <v>44120</v>
       </c>
       <c r="B126" t="n">
-        <v>45.67477150382671</v>
+        <v>45.67561221889184</v>
       </c>
       <c r="C126" t="n">
-        <v>4.582780217819449</v>
+        <v>4.582489271814482</v>
       </c>
       <c r="D126" t="n">
         <v>1</v>
@@ -2209,10 +2209,10 @@
         <v>44127</v>
       </c>
       <c r="B127" t="n">
-        <v>46.18732440943237</v>
+        <v>46.18806668973013</v>
       </c>
       <c r="C127" t="n">
-        <v>4.187176160028533</v>
+        <v>4.186936456753158</v>
       </c>
       <c r="D127" t="n">
         <v>1</v>
@@ -2223,10 +2223,10 @@
         <v>44134</v>
       </c>
       <c r="B128" t="n">
-        <v>46.16505704216924</v>
+        <v>46.16580856091651</v>
       </c>
       <c r="C128" t="n">
-        <v>4.376395007733013</v>
+        <v>4.376147126032855</v>
       </c>
       <c r="D128" t="n">
         <v>1</v>
@@ -2237,10 +2237,10 @@
         <v>44141</v>
       </c>
       <c r="B129" t="n">
-        <v>44.33372564264204</v>
+        <v>44.33432590372473</v>
       </c>
       <c r="C129" t="n">
-        <v>5.266992484429675</v>
+        <v>5.266831594629395</v>
       </c>
       <c r="D129" t="n">
         <v>1</v>
@@ -2251,10 +2251,10 @@
         <v>44148</v>
       </c>
       <c r="B130" t="n">
-        <v>42.63938221903155</v>
+        <v>42.64004478017489</v>
       </c>
       <c r="C130" t="n">
-        <v>4.091450541878215</v>
+        <v>4.09131780351676</v>
       </c>
       <c r="D130" t="n">
         <v>1</v>
@@ -2265,10 +2265,10 @@
         <v>44155</v>
       </c>
       <c r="B131" t="n">
-        <v>43.34893985599535</v>
+        <v>43.34948044919346</v>
       </c>
       <c r="C131" t="n">
-        <v>4.335130596466704</v>
+        <v>4.33495899602101</v>
       </c>
       <c r="D131" t="n">
         <v>1</v>
@@ -2279,10 +2279,10 @@
         <v>44162</v>
       </c>
       <c r="B132" t="n">
-        <v>42.49551744073682</v>
+        <v>42.49594603334941</v>
       </c>
       <c r="C132" t="n">
-        <v>4.881657523111284</v>
+        <v>4.881379708176891</v>
       </c>
       <c r="D132" t="n">
         <v>1</v>
@@ -2293,10 +2293,10 @@
         <v>44169</v>
       </c>
       <c r="B133" t="n">
-        <v>43.82938406774885</v>
+        <v>43.83011465782937</v>
       </c>
       <c r="C133" t="n">
-        <v>2.673462930783707</v>
+        <v>2.673080739879333</v>
       </c>
       <c r="D133" t="n">
         <v>1</v>
@@ -2307,10 +2307,10 @@
         <v>44176</v>
       </c>
       <c r="B134" t="n">
-        <v>45.01270450979314</v>
+        <v>45.01362819281874</v>
       </c>
       <c r="C134" t="n">
-        <v>2.641971504277378</v>
+        <v>2.641835049597381</v>
       </c>
       <c r="D134" t="n">
         <v>1</v>
@@ -2321,10 +2321,10 @@
         <v>44183</v>
       </c>
       <c r="B135" t="n">
-        <v>45.03791226423593</v>
+        <v>45.03874931163569</v>
       </c>
       <c r="C135" t="n">
-        <v>2.845727852587776</v>
+        <v>2.845455337999036</v>
       </c>
       <c r="D135" t="n">
         <v>1</v>
@@ -2335,10 +2335,10 @@
         <v>44190</v>
       </c>
       <c r="B136" t="n">
-        <v>44.84593440049309</v>
+        <v>44.8466721779125</v>
       </c>
       <c r="C136" t="n">
-        <v>3.330140549312527</v>
+        <v>3.329709860225957</v>
       </c>
       <c r="D136" t="n">
         <v>1</v>
@@ -2349,10 +2349,10 @@
         <v>44197</v>
       </c>
       <c r="B137" t="n">
-        <v>43.71790296063973</v>
+        <v>43.71925660659534</v>
       </c>
       <c r="C137" t="n">
-        <v>2.645194430422324</v>
+        <v>2.644868325059025</v>
       </c>
       <c r="D137" t="n">
         <v>1</v>
@@ -2363,10 +2363,10 @@
         <v>44204</v>
       </c>
       <c r="B138" t="n">
-        <v>43.8367585976093</v>
+        <v>43.83747068310324</v>
       </c>
       <c r="C138" t="n">
-        <v>2.955526209042018</v>
+        <v>2.955191805515859</v>
       </c>
       <c r="D138" t="n">
         <v>1</v>
@@ -2377,10 +2377,10 @@
         <v>44211</v>
       </c>
       <c r="B139" t="n">
-        <v>43.64767453357907</v>
+        <v>43.64836044172184</v>
       </c>
       <c r="C139" t="n">
-        <v>3.133735555605968</v>
+        <v>3.133412903954196</v>
       </c>
       <c r="D139" t="n">
         <v>1</v>
@@ -2391,10 +2391,10 @@
         <v>44218</v>
       </c>
       <c r="B140" t="n">
-        <v>43.7075438227537</v>
+        <v>43.7082569792821</v>
       </c>
       <c r="C140" t="n">
-        <v>3.249425500930009</v>
+        <v>3.249092194352718</v>
       </c>
       <c r="D140" t="n">
         <v>1</v>
@@ -2405,10 +2405,10 @@
         <v>44225</v>
       </c>
       <c r="B141" t="n">
-        <v>44.19554298787576</v>
+        <v>44.19629468697021</v>
       </c>
       <c r="C141" t="n">
-        <v>3.473850312247555</v>
+        <v>3.473501600205101</v>
       </c>
       <c r="D141" t="n">
         <v>1</v>
@@ -2419,10 +2419,10 @@
         <v>44232</v>
       </c>
       <c r="B142" t="n">
-        <v>43.55380784875353</v>
+        <v>43.55445045798538</v>
       </c>
       <c r="C142" t="n">
-        <v>3.506242555615642</v>
+        <v>3.505926505915215</v>
       </c>
       <c r="D142" t="n">
         <v>1</v>
@@ -2433,10 +2433,10 @@
         <v>44239</v>
       </c>
       <c r="B143" t="n">
-        <v>43.39827583848221</v>
+        <v>43.3989380932056</v>
       </c>
       <c r="C143" t="n">
-        <v>3.558177863745339</v>
+        <v>3.557855794935612</v>
       </c>
       <c r="D143" t="n">
         <v>1</v>
@@ -2447,10 +2447,10 @@
         <v>44246</v>
       </c>
       <c r="B144" t="n">
-        <v>42.15797446993817</v>
+        <v>42.15892612332724</v>
       </c>
       <c r="C144" t="n">
-        <v>4.113020075460337</v>
+        <v>4.112600853239971</v>
       </c>
       <c r="D144" t="n">
         <v>1</v>
@@ -2461,10 +2461,10 @@
         <v>44253</v>
       </c>
       <c r="B145" t="n">
-        <v>43.58356020123727</v>
+        <v>43.58431444769146</v>
       </c>
       <c r="C145" t="n">
-        <v>3.781360614141613</v>
+        <v>3.781071357657252</v>
       </c>
       <c r="D145" t="n">
         <v>1</v>
@@ -2475,10 +2475,10 @@
         <v>44260</v>
       </c>
       <c r="B146" t="n">
-        <v>56.90081524759312</v>
+        <v>56.90095747870546</v>
       </c>
       <c r="C146" t="n">
-        <v>8.359392042947324</v>
+        <v>8.360040489905089</v>
       </c>
       <c r="D146" t="n">
         <v>1</v>
@@ -2489,10 +2489,10 @@
         <v>44267</v>
       </c>
       <c r="B147" t="n">
-        <v>56.7403378928424</v>
+        <v>56.74017368137576</v>
       </c>
       <c r="C147" t="n">
-        <v>8.051022393594257</v>
+        <v>8.05163198550742</v>
       </c>
       <c r="D147" t="n">
         <v>1</v>
@@ -2503,10 +2503,10 @@
         <v>44274</v>
       </c>
       <c r="B148" t="n">
-        <v>56.71324933213672</v>
+        <v>56.71305409049125</v>
       </c>
       <c r="C148" t="n">
-        <v>7.680222654136458</v>
+        <v>7.681097755033994</v>
       </c>
       <c r="D148" t="n">
         <v>1</v>
@@ -2517,10 +2517,10 @@
         <v>44281</v>
       </c>
       <c r="B149" t="n">
-        <v>44.76070950726604</v>
+        <v>44.76127369758095</v>
       </c>
       <c r="C149" t="n">
-        <v>4.131901092743408</v>
+        <v>4.131791412470365</v>
       </c>
       <c r="D149" t="n">
         <v>1</v>
@@ -2531,10 +2531,10 @@
         <v>44288</v>
       </c>
       <c r="B150" t="n">
-        <v>44.43359733625564</v>
+        <v>44.43425157477884</v>
       </c>
       <c r="C150" t="n">
-        <v>3.965389053514107</v>
+        <v>3.965250425442131</v>
       </c>
       <c r="D150" t="n">
         <v>1</v>
@@ -2545,10 +2545,10 @@
         <v>44295</v>
       </c>
       <c r="B151" t="n">
-        <v>44.71037118416186</v>
+        <v>44.71097169223165</v>
       </c>
       <c r="C151" t="n">
-        <v>3.720197665492738</v>
+        <v>3.720081094428998</v>
       </c>
       <c r="D151" t="n">
         <v>1</v>
@@ -2559,10 +2559,10 @@
         <v>44302</v>
       </c>
       <c r="B152" t="n">
-        <v>44.69894501346034</v>
+        <v>44.69962130786497</v>
       </c>
       <c r="C152" t="n">
-        <v>3.55679675356185</v>
+        <v>3.556625420228079</v>
       </c>
       <c r="D152" t="n">
         <v>1</v>
@@ -2573,10 +2573,10 @@
         <v>44309</v>
       </c>
       <c r="B153" t="n">
-        <v>45.24046163604648</v>
+        <v>45.24078780372398</v>
       </c>
       <c r="C153" t="n">
-        <v>3.464882307751265</v>
+        <v>3.464758219919217</v>
       </c>
       <c r="D153" t="n">
         <v>1</v>
@@ -2587,10 +2587,10 @@
         <v>44316</v>
       </c>
       <c r="B154" t="n">
-        <v>43.89746118253637</v>
+        <v>43.89792995173406</v>
       </c>
       <c r="C154" t="n">
-        <v>3.885294934642153</v>
+        <v>3.885075084075585</v>
       </c>
       <c r="D154" t="n">
         <v>1</v>
@@ -2601,10 +2601,10 @@
         <v>44323</v>
       </c>
       <c r="B155" t="n">
-        <v>43.90252123348055</v>
+        <v>43.90341905655487</v>
       </c>
       <c r="C155" t="n">
-        <v>5.903271631847851</v>
+        <v>5.903096157613416</v>
       </c>
       <c r="D155" t="n">
         <v>1</v>
@@ -2615,10 +2615,10 @@
         <v>44330</v>
       </c>
       <c r="B156" t="n">
-        <v>44.63670644016319</v>
+        <v>44.63748202397556</v>
       </c>
       <c r="C156" t="n">
-        <v>6.001680630154768</v>
+        <v>6.001484638708326</v>
       </c>
       <c r="D156" t="n">
         <v>1</v>
@@ -2629,10 +2629,10 @@
         <v>44337</v>
       </c>
       <c r="B157" t="n">
-        <v>44.5238491715462</v>
+        <v>44.52455956417384</v>
       </c>
       <c r="C157" t="n">
-        <v>5.938085056689438</v>
+        <v>5.937897987710896</v>
       </c>
       <c r="D157" t="n">
         <v>1</v>
@@ -2643,10 +2643,10 @@
         <v>44344</v>
       </c>
       <c r="B158" t="n">
-        <v>43.79122693880642</v>
+        <v>43.79177020410773</v>
       </c>
       <c r="C158" t="n">
-        <v>5.927974738355036</v>
+        <v>5.927809781664179</v>
       </c>
       <c r="D158" t="n">
         <v>1</v>
@@ -2657,10 +2657,10 @@
         <v>44351</v>
       </c>
       <c r="B159" t="n">
-        <v>43.79632693200083</v>
+        <v>43.79695670038211</v>
       </c>
       <c r="C159" t="n">
-        <v>5.80370506458017</v>
+        <v>5.803552831883858</v>
       </c>
       <c r="D159" t="n">
         <v>1</v>
@@ -2671,10 +2671,10 @@
         <v>44358</v>
       </c>
       <c r="B160" t="n">
-        <v>44.47059506695365</v>
+        <v>44.47101115468941</v>
       </c>
       <c r="C160" t="n">
-        <v>6.926090638418149</v>
+        <v>6.925949792279797</v>
       </c>
       <c r="D160" t="n">
         <v>1</v>
@@ -2685,10 +2685,10 @@
         <v>44365</v>
       </c>
       <c r="B161" t="n">
-        <v>43.28037030460587</v>
+        <v>43.28051612511197</v>
       </c>
       <c r="C161" t="n">
-        <v>5.747933565986322</v>
+        <v>5.747754278674046</v>
       </c>
       <c r="D161" t="n">
         <v>1</v>
@@ -2699,10 +2699,10 @@
         <v>44372</v>
       </c>
       <c r="B162" t="n">
-        <v>43.46985827920962</v>
+        <v>43.46996123845963</v>
       </c>
       <c r="C162" t="n">
-        <v>4.683391013439651</v>
+        <v>4.683185827660455</v>
       </c>
       <c r="D162" t="n">
         <v>1</v>
@@ -2713,10 +2713,10 @@
         <v>44379</v>
       </c>
       <c r="B163" t="n">
-        <v>43.53452586094371</v>
+        <v>43.53460470022936</v>
       </c>
       <c r="C163" t="n">
-        <v>4.85818439111257</v>
+        <v>4.857979580371873</v>
       </c>
       <c r="D163" t="n">
         <v>1</v>
@@ -2727,10 +2727,10 @@
         <v>44386</v>
       </c>
       <c r="B164" t="n">
-        <v>43.28445411126241</v>
+        <v>43.28460032662452</v>
       </c>
       <c r="C164" t="n">
-        <v>5.101624310967964</v>
+        <v>5.101405252278647</v>
       </c>
       <c r="D164" t="n">
         <v>1</v>
@@ -2741,10 +2741,10 @@
         <v>44393</v>
       </c>
       <c r="B165" t="n">
-        <v>41.52822250610372</v>
+        <v>41.52815146459199</v>
       </c>
       <c r="C165" t="n">
-        <v>4.187722010709061</v>
+        <v>4.187468856953018</v>
       </c>
       <c r="D165" t="n">
         <v>1</v>
@@ -2755,10 +2755,10 @@
         <v>44400</v>
       </c>
       <c r="B166" t="n">
-        <v>41.83608793809762</v>
+        <v>41.83609318155632</v>
       </c>
       <c r="C166" t="n">
-        <v>3.808305716424155</v>
+        <v>3.808226168761021</v>
       </c>
       <c r="D166" t="n">
         <v>1</v>
@@ -2769,10 +2769,10 @@
         <v>44407</v>
       </c>
       <c r="B167" t="n">
-        <v>41.15714412379103</v>
+        <v>41.15723561069464</v>
       </c>
       <c r="C167" t="n">
-        <v>3.434297068207301</v>
+        <v>3.434261713347289</v>
       </c>
       <c r="D167" t="n">
         <v>1</v>
@@ -2783,10 +2783,10 @@
         <v>44414</v>
       </c>
       <c r="B168" t="n">
-        <v>44.28846207980877</v>
+        <v>44.28849529590832</v>
       </c>
       <c r="C168" t="n">
-        <v>6.628712424756261</v>
+        <v>6.628595355702441</v>
       </c>
       <c r="D168" t="n">
         <v>1</v>
@@ -2797,10 +2797,10 @@
         <v>44421</v>
       </c>
       <c r="B169" t="n">
-        <v>43.47137496939613</v>
+        <v>43.47145520380594</v>
       </c>
       <c r="C169" t="n">
-        <v>6.165990497069429</v>
+        <v>6.165916466428053</v>
       </c>
       <c r="D169" t="n">
         <v>1</v>
@@ -2811,10 +2811,10 @@
         <v>44428</v>
       </c>
       <c r="B170" t="n">
-        <v>43.57422554411426</v>
+        <v>43.574304279876</v>
       </c>
       <c r="C170" t="n">
-        <v>6.30728118770272</v>
+        <v>6.307187264586994</v>
       </c>
       <c r="D170" t="n">
         <v>1</v>
@@ -2825,10 +2825,10 @@
         <v>44435</v>
       </c>
       <c r="B171" t="n">
-        <v>43.67403913325819</v>
+        <v>43.67406091358171</v>
       </c>
       <c r="C171" t="n">
-        <v>6.296687145208081</v>
+        <v>6.296603866178734</v>
       </c>
       <c r="D171" t="n">
         <v>1</v>
@@ -2839,10 +2839,10 @@
         <v>44442</v>
       </c>
       <c r="B172" t="n">
-        <v>43.6613335321294</v>
+        <v>43.66137992085746</v>
       </c>
       <c r="C172" t="n">
-        <v>5.135917932096637</v>
+        <v>5.135827045344336</v>
       </c>
       <c r="D172" t="n">
         <v>1</v>
@@ -2853,10 +2853,10 @@
         <v>44449</v>
       </c>
       <c r="B173" t="n">
-        <v>43.28724849624991</v>
+        <v>43.28735787576977</v>
       </c>
       <c r="C173" t="n">
-        <v>5.243477698629008</v>
+        <v>5.243393653229959</v>
       </c>
       <c r="D173" t="n">
         <v>1</v>
@@ -2867,10 +2867,10 @@
         <v>44456</v>
       </c>
       <c r="B174" t="n">
-        <v>43.25922171837893</v>
+        <v>43.25929103620646</v>
       </c>
       <c r="C174" t="n">
-        <v>5.228719014512518</v>
+        <v>5.228614783326906</v>
       </c>
       <c r="D174" t="n">
         <v>1</v>
@@ -2881,10 +2881,10 @@
         <v>44463</v>
       </c>
       <c r="B175" t="n">
-        <v>43.11680141963971</v>
+        <v>43.11677915883276</v>
       </c>
       <c r="C175" t="n">
-        <v>5.205346175844386</v>
+        <v>5.205260163586822</v>
       </c>
       <c r="D175" t="n">
         <v>1</v>
@@ -2895,10 +2895,10 @@
         <v>44470</v>
       </c>
       <c r="B176" t="n">
-        <v>43.2895528167997</v>
+        <v>43.28960593555141</v>
       </c>
       <c r="C176" t="n">
-        <v>5.154474355442876</v>
+        <v>5.154415700254376</v>
       </c>
       <c r="D176" t="n">
         <v>1</v>
@@ -2909,10 +2909,10 @@
         <v>44477</v>
       </c>
       <c r="B177" t="n">
-        <v>43.77988667253309</v>
+        <v>43.77996347872266</v>
       </c>
       <c r="C177" t="n">
-        <v>5.468051612082142</v>
+        <v>5.467914868681697</v>
       </c>
       <c r="D177" t="n">
         <v>1</v>
@@ -2923,10 +2923,10 @@
         <v>44484</v>
       </c>
       <c r="B178" t="n">
-        <v>43.59953795379058</v>
+        <v>43.59965373314915</v>
       </c>
       <c r="C178" t="n">
-        <v>5.440117491695049</v>
+        <v>5.43998088201904</v>
       </c>
       <c r="D178" t="n">
         <v>1</v>
@@ -2937,10 +2937,10 @@
         <v>44491</v>
       </c>
       <c r="B179" t="n">
-        <v>43.27856943121692</v>
+        <v>43.27878782756103</v>
       </c>
       <c r="C179" t="n">
-        <v>5.157587587320176</v>
+        <v>5.15745471379018</v>
       </c>
       <c r="D179" t="n">
         <v>1</v>
@@ -2951,10 +2951,10 @@
         <v>44498</v>
       </c>
       <c r="B180" t="n">
-        <v>44.45311333947364</v>
+        <v>44.45325705292453</v>
       </c>
       <c r="C180" t="n">
-        <v>5.632800516577436</v>
+        <v>5.632584014331153</v>
       </c>
       <c r="D180" t="n">
         <v>1</v>
@@ -2965,10 +2965,10 @@
         <v>44505</v>
       </c>
       <c r="B181" t="n">
-        <v>44.06752703478767</v>
+        <v>44.06784231199794</v>
       </c>
       <c r="C181" t="n">
-        <v>5.201239899317914</v>
+        <v>5.201087995627232</v>
       </c>
       <c r="D181" t="n">
         <v>1</v>
@@ -2979,10 +2979,10 @@
         <v>44512</v>
       </c>
       <c r="B182" t="n">
-        <v>44.10813666979281</v>
+        <v>44.10847353198568</v>
       </c>
       <c r="C182" t="n">
-        <v>4.923792755285723</v>
+        <v>4.92363269361614</v>
       </c>
       <c r="D182" t="n">
         <v>1</v>
@@ -2993,10 +2993,10 @@
         <v>44519</v>
       </c>
       <c r="B183" t="n">
-        <v>44.45990737229364</v>
+        <v>44.46036009166416</v>
       </c>
       <c r="C183" t="n">
-        <v>4.352885901017048</v>
+        <v>4.352761366433501</v>
       </c>
       <c r="D183" t="n">
         <v>1</v>
@@ -3007,10 +3007,10 @@
         <v>44526</v>
       </c>
       <c r="B184" t="n">
-        <v>45.56530404445246</v>
+        <v>45.56562654098624</v>
       </c>
       <c r="C184" t="n">
-        <v>4.898184948363613</v>
+        <v>4.898020445417184</v>
       </c>
       <c r="D184" t="n">
         <v>1</v>
@@ -3021,10 +3021,10 @@
         <v>44533</v>
       </c>
       <c r="B185" t="n">
-        <v>46.6818168661163</v>
+        <v>46.68216752806477</v>
       </c>
       <c r="C185" t="n">
-        <v>5.630899940279899</v>
+        <v>5.630682790958424</v>
       </c>
       <c r="D185" t="n">
         <v>1</v>
@@ -3035,10 +3035,10 @@
         <v>44540</v>
       </c>
       <c r="B186" t="n">
-        <v>46.24741467503519</v>
+        <v>46.24778934105169</v>
       </c>
       <c r="C186" t="n">
-        <v>5.527678023714254</v>
+        <v>5.527385453815601</v>
       </c>
       <c r="D186" t="n">
         <v>1</v>
@@ -3049,10 +3049,10 @@
         <v>44547</v>
       </c>
       <c r="B187" t="n">
-        <v>46.68605175200972</v>
+        <v>46.68653453917364</v>
       </c>
       <c r="C187" t="n">
-        <v>5.32819588805346</v>
+        <v>5.327972187098617</v>
       </c>
       <c r="D187" t="n">
         <v>1</v>
@@ -3063,10 +3063,10 @@
         <v>44554</v>
       </c>
       <c r="B188" t="n">
-        <v>47.76024799785142</v>
+        <v>47.76073345949199</v>
       </c>
       <c r="C188" t="n">
-        <v>5.668410933745406</v>
+        <v>5.668423086705728</v>
       </c>
       <c r="D188" t="n">
         <v>1</v>
@@ -3077,10 +3077,10 @@
         <v>44561</v>
       </c>
       <c r="B189" t="n">
-        <v>49.45327911564251</v>
+        <v>49.45369673309111</v>
       </c>
       <c r="C189" t="n">
-        <v>8.306088013745471</v>
+        <v>8.306041812979576</v>
       </c>
       <c r="D189" t="n">
         <v>1</v>
@@ -3091,10 +3091,10 @@
         <v>44568</v>
       </c>
       <c r="B190" t="n">
-        <v>48.13825916639465</v>
+        <v>48.13866492016487</v>
       </c>
       <c r="C190" t="n">
-        <v>7.016040184456823</v>
+        <v>7.016033726791388</v>
       </c>
       <c r="D190" t="n">
         <v>1</v>
@@ -3105,10 +3105,10 @@
         <v>44575</v>
       </c>
       <c r="B191" t="n">
-        <v>47.67017570826371</v>
+        <v>47.67057455254463</v>
       </c>
       <c r="C191" t="n">
-        <v>6.379482489038077</v>
+        <v>6.37948106082086</v>
       </c>
       <c r="D191" t="n">
         <v>1</v>
@@ -3119,10 +3119,10 @@
         <v>44582</v>
       </c>
       <c r="B192" t="n">
-        <v>47.87331451017801</v>
+        <v>47.87374804649225</v>
       </c>
       <c r="C192" t="n">
-        <v>6.121875914355769</v>
+        <v>6.121914988168655</v>
       </c>
       <c r="D192" t="n">
         <v>1</v>
@@ -3133,10 +3133,10 @@
         <v>44589</v>
       </c>
       <c r="B193" t="n">
-        <v>47.78310723929843</v>
+        <v>47.78361294123985</v>
       </c>
       <c r="C193" t="n">
-        <v>5.858075021167434</v>
+        <v>5.858054460797173</v>
       </c>
       <c r="D193" t="n">
         <v>1</v>
@@ -3147,10 +3147,10 @@
         <v>44596</v>
       </c>
       <c r="B194" t="n">
-        <v>47.40691541148194</v>
+        <v>47.40737743693477</v>
       </c>
       <c r="C194" t="n">
-        <v>5.573739941682323</v>
+        <v>5.573668888914858</v>
       </c>
       <c r="D194" t="n">
         <v>1</v>
@@ -3161,10 +3161,10 @@
         <v>44603</v>
       </c>
       <c r="B195" t="n">
-        <v>47.15709330144674</v>
+        <v>47.1575893556994</v>
       </c>
       <c r="C195" t="n">
-        <v>5.425538722693734</v>
+        <v>5.425470092162612</v>
       </c>
       <c r="D195" t="n">
         <v>1</v>
@@ -3175,10 +3175,10 @@
         <v>44610</v>
       </c>
       <c r="B196" t="n">
-        <v>46.54137415812806</v>
+        <v>46.5419953670764</v>
       </c>
       <c r="C196" t="n">
-        <v>5.338935800874714</v>
+        <v>5.338900869504201</v>
       </c>
       <c r="D196" t="n">
         <v>1</v>
@@ -3189,10 +3189,10 @@
         <v>44617</v>
       </c>
       <c r="B197" t="n">
-        <v>46.8873706706468</v>
+        <v>46.88795621972477</v>
       </c>
       <c r="C197" t="n">
-        <v>5.721582838424361</v>
+        <v>5.721543999226414</v>
       </c>
       <c r="D197" t="n">
         <v>1</v>
@@ -3203,10 +3203,10 @@
         <v>44624</v>
       </c>
       <c r="B198" t="n">
-        <v>47.29980151624387</v>
+        <v>47.30036345005417</v>
       </c>
       <c r="C198" t="n">
-        <v>5.573738817423171</v>
+        <v>5.573692703349126</v>
       </c>
       <c r="D198" t="n">
         <v>1</v>
@@ -3217,10 +3217,10 @@
         <v>44631</v>
       </c>
       <c r="B199" t="n">
-        <v>47.63087156121205</v>
+        <v>47.63149066439808</v>
       </c>
       <c r="C199" t="n">
-        <v>5.940760653718679</v>
+        <v>5.940720589371833</v>
       </c>
       <c r="D199" t="n">
         <v>1</v>
@@ -3231,10 +3231,10 @@
         <v>44638</v>
       </c>
       <c r="B200" t="n">
-        <v>47.15354434175316</v>
+        <v>47.1540433819254</v>
       </c>
       <c r="C200" t="n">
-        <v>5.151461166570454</v>
+        <v>5.15138291178179</v>
       </c>
       <c r="D200" t="n">
         <v>1</v>
@@ -3245,10 +3245,10 @@
         <v>44645</v>
       </c>
       <c r="B201" t="n">
-        <v>47.40787238128636</v>
+        <v>47.40831825780452</v>
       </c>
       <c r="C201" t="n">
-        <v>5.501726333889352</v>
+        <v>5.501663763164514</v>
       </c>
       <c r="D201" t="n">
         <v>1</v>
@@ -3259,10 +3259,10 @@
         <v>44652</v>
       </c>
       <c r="B202" t="n">
-        <v>47.74208700123932</v>
+        <v>47.7426152960604</v>
       </c>
       <c r="C202" t="n">
-        <v>6.233375600129012</v>
+        <v>6.233338489382094</v>
       </c>
       <c r="D202" t="n">
         <v>1</v>
@@ -3273,10 +3273,10 @@
         <v>44659</v>
       </c>
       <c r="B203" t="n">
-        <v>48.08158587027044</v>
+        <v>48.08197363720996</v>
       </c>
       <c r="C203" t="n">
-        <v>6.841653728123253</v>
+        <v>6.8416021799956</v>
       </c>
       <c r="D203" t="n">
         <v>1</v>
@@ -3287,10 +3287,10 @@
         <v>44666</v>
       </c>
       <c r="B204" t="n">
-        <v>47.63133488188874</v>
+        <v>47.63158766354103</v>
       </c>
       <c r="C204" t="n">
-        <v>6.517326710020892</v>
+        <v>6.517315372056437</v>
       </c>
       <c r="D204" t="n">
         <v>1</v>
@@ -3301,10 +3301,10 @@
         <v>44673</v>
       </c>
       <c r="B205" t="n">
-        <v>48.04131299881355</v>
+        <v>48.04147038127807</v>
       </c>
       <c r="C205" t="n">
-        <v>6.396328351700689</v>
+        <v>6.396298848837113</v>
       </c>
       <c r="D205" t="n">
         <v>1</v>
@@ -3315,10 +3315,10 @@
         <v>44680</v>
       </c>
       <c r="B206" t="n">
-        <v>48.31014678788389</v>
+        <v>48.31029188908289</v>
       </c>
       <c r="C206" t="n">
-        <v>6.546643430169119</v>
+        <v>6.546613063169805</v>
       </c>
       <c r="D206" t="n">
         <v>1</v>
@@ -3329,10 +3329,10 @@
         <v>44687</v>
       </c>
       <c r="B207" t="n">
-        <v>46.54870766397648</v>
+        <v>46.54879931380676</v>
       </c>
       <c r="C207" t="n">
-        <v>6.536148636861483</v>
+        <v>6.536139681152452</v>
       </c>
       <c r="D207" t="n">
         <v>1</v>
@@ -3343,10 +3343,10 @@
         <v>44694</v>
       </c>
       <c r="B208" t="n">
-        <v>46.75187116986719</v>
+        <v>46.75195895437773</v>
       </c>
       <c r="C208" t="n">
-        <v>6.652312534706782</v>
+        <v>6.652275083317985</v>
       </c>
       <c r="D208" t="n">
         <v>1</v>
@@ -3357,10 +3357,10 @@
         <v>44701</v>
       </c>
       <c r="B209" t="n">
-        <v>46.91781563581327</v>
+        <v>46.91783726215656</v>
       </c>
       <c r="C209" t="n">
-        <v>6.232204060582301</v>
+        <v>6.232221287932333</v>
       </c>
       <c r="D209" t="n">
         <v>1</v>
@@ -3371,10 +3371,10 @@
         <v>44708</v>
       </c>
       <c r="B210" t="n">
-        <v>46.53662953811769</v>
+        <v>46.53660485425531</v>
       </c>
       <c r="C210" t="n">
-        <v>5.549863528424654</v>
+        <v>5.549921548041087</v>
       </c>
       <c r="D210" t="n">
         <v>1</v>
@@ -3385,10 +3385,10 @@
         <v>44715</v>
       </c>
       <c r="B211" t="n">
-        <v>46.60341375145068</v>
+        <v>46.60346815473141</v>
       </c>
       <c r="C211" t="n">
-        <v>5.578722427910218</v>
+        <v>5.578675788406072</v>
       </c>
       <c r="D211" t="n">
         <v>1</v>
@@ -3399,10 +3399,10 @@
         <v>44722</v>
       </c>
       <c r="B212" t="n">
-        <v>46.50390942245045</v>
+        <v>46.50346022074837</v>
       </c>
       <c r="C212" t="n">
-        <v>5.767527276950382</v>
+        <v>5.767311057450654</v>
       </c>
       <c r="D212" t="n">
         <v>1</v>
@@ -3413,10 +3413,10 @@
         <v>44729</v>
       </c>
       <c r="B213" t="n">
-        <v>46.53719571472806</v>
+        <v>46.53707921598892</v>
       </c>
       <c r="C213" t="n">
-        <v>5.675564200600322</v>
+        <v>5.67538950526243</v>
       </c>
       <c r="D213" t="n">
         <v>1</v>
@@ -3427,10 +3427,10 @@
         <v>44736</v>
       </c>
       <c r="B214" t="n">
-        <v>46.36917701308207</v>
+        <v>46.36909685822869</v>
       </c>
       <c r="C214" t="n">
-        <v>5.855155478489719</v>
+        <v>5.854986890661624</v>
       </c>
       <c r="D214" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>44743</v>
       </c>
       <c r="B215" t="n">
-        <v>46.04976531414798</v>
+        <v>46.04966310923142</v>
       </c>
       <c r="C215" t="n">
-        <v>5.906951187868446</v>
+        <v>5.906870733490903</v>
       </c>
       <c r="D215" t="n">
         <v>0</v>
@@ -3455,10 +3455,10 @@
         <v>44750</v>
       </c>
       <c r="B216" t="n">
-        <v>45.9162911215329</v>
+        <v>45.91614317194342</v>
       </c>
       <c r="C216" t="n">
-        <v>6.195094427126048</v>
+        <v>6.194984451999415</v>
       </c>
       <c r="D216" t="n">
         <v>0</v>
@@ -3469,10 +3469,10 @@
         <v>44757</v>
       </c>
       <c r="B217" t="n">
-        <v>45.05966609907639</v>
+        <v>45.05991952721173</v>
       </c>
       <c r="C217" t="n">
-        <v>6.93567645152105</v>
+        <v>6.935621832336115</v>
       </c>
       <c r="D217" t="n">
         <v>0</v>
@@ -3483,10 +3483,10 @@
         <v>44764</v>
       </c>
       <c r="B218" t="n">
-        <v>45.41554030278456</v>
+        <v>45.41584317742902</v>
       </c>
       <c r="C218" t="n">
-        <v>7.003177549848887</v>
+        <v>7.003147803696184</v>
       </c>
       <c r="D218" t="n">
         <v>0</v>
@@ -3497,10 +3497,10 @@
         <v>44771</v>
       </c>
       <c r="B219" t="n">
-        <v>44.65692980670506</v>
+        <v>44.65723577029908</v>
       </c>
       <c r="C219" t="n">
-        <v>6.101562684402055</v>
+        <v>6.101509130823334</v>
       </c>
       <c r="D219" t="n">
         <v>0</v>
@@ -3511,10 +3511,10 @@
         <v>44778</v>
       </c>
       <c r="B220" t="n">
-        <v>44.70148284249671</v>
+        <v>44.70176686378834</v>
       </c>
       <c r="C220" t="n">
-        <v>5.806971451072167</v>
+        <v>5.806919408699519</v>
       </c>
       <c r="D220" t="n">
         <v>0</v>
@@ -3525,10 +3525,10 @@
         <v>44785</v>
       </c>
       <c r="B221" t="n">
-        <v>44.93484255056268</v>
+        <v>44.9352400779421</v>
       </c>
       <c r="C221" t="n">
-        <v>5.898592393936978</v>
+        <v>5.898626476239579</v>
       </c>
       <c r="D221" t="n">
         <v>0</v>
@@ -3539,10 +3539,10 @@
         <v>44792</v>
       </c>
       <c r="B222" t="n">
-        <v>44.49609579247535</v>
+        <v>44.4964596494688</v>
       </c>
       <c r="C222" t="n">
-        <v>5.571025903934659</v>
+        <v>5.571035415780567</v>
       </c>
       <c r="D222" t="n">
         <v>0</v>
@@ -3553,10 +3553,10 @@
         <v>44799</v>
       </c>
       <c r="B223" t="n">
-        <v>44.83493462727161</v>
+        <v>44.83517584937215</v>
       </c>
       <c r="C223" t="n">
-        <v>5.96152383761292</v>
+        <v>5.961391924539425</v>
       </c>
       <c r="D223" t="n">
         <v>0</v>
@@ -3567,10 +3567,10 @@
         <v>44806</v>
       </c>
       <c r="B224" t="n">
-        <v>44.63664298249867</v>
+        <v>44.63694042944697</v>
       </c>
       <c r="C224" t="n">
-        <v>5.874895229534815</v>
+        <v>5.87480212133176</v>
       </c>
       <c r="D224" t="n">
         <v>0</v>
@@ -3581,10 +3581,10 @@
         <v>44813</v>
       </c>
       <c r="B225" t="n">
-        <v>44.49765714568021</v>
+        <v>44.49796378135983</v>
       </c>
       <c r="C225" t="n">
-        <v>5.852568303436604</v>
+        <v>5.852652772550802</v>
       </c>
       <c r="D225" t="n">
         <v>0</v>
@@ -3595,10 +3595,10 @@
         <v>44820</v>
       </c>
       <c r="B226" t="n">
-        <v>44.54162114314641</v>
+        <v>44.54176453336328</v>
       </c>
       <c r="C226" t="n">
-        <v>6.595877674909874</v>
+        <v>6.59592554652353</v>
       </c>
       <c r="D226" t="n">
         <v>0</v>
@@ -3609,10 +3609,10 @@
         <v>44827</v>
       </c>
       <c r="B227" t="n">
-        <v>44.96998707828578</v>
+        <v>44.97011403699207</v>
       </c>
       <c r="C227" t="n">
-        <v>6.836807260501006</v>
+        <v>6.836797525790497</v>
       </c>
       <c r="D227" t="n">
         <v>0</v>
@@ -3623,10 +3623,10 @@
         <v>44834</v>
       </c>
       <c r="B228" t="n">
-        <v>43.07664736856827</v>
+        <v>43.07700801736704</v>
       </c>
       <c r="C228" t="n">
-        <v>6.30046004363418</v>
+        <v>6.30060519863712</v>
       </c>
       <c r="D228" t="n">
         <v>0</v>
@@ -3637,10 +3637,10 @@
         <v>44841</v>
       </c>
       <c r="B229" t="n">
-        <v>42.84880319916677</v>
+        <v>42.84922934062016</v>
       </c>
       <c r="C229" t="n">
-        <v>6.170088218212177</v>
+        <v>6.170220102712403</v>
       </c>
       <c r="D229" t="n">
         <v>0</v>
@@ -3651,10 +3651,10 @@
         <v>44848</v>
       </c>
       <c r="B230" t="n">
-        <v>41.99187588001937</v>
+        <v>41.99223355831197</v>
       </c>
       <c r="C230" t="n">
-        <v>5.75494736015207</v>
+        <v>5.755065796163758</v>
       </c>
       <c r="D230" t="n">
         <v>0</v>
@@ -3665,10 +3665,10 @@
         <v>44855</v>
       </c>
       <c r="B231" t="n">
-        <v>42.23157363184029</v>
+        <v>42.23203630210434</v>
       </c>
       <c r="C231" t="n">
-        <v>5.85201811569509</v>
+        <v>5.852180591959707</v>
       </c>
       <c r="D231" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>44862</v>
       </c>
       <c r="B232" t="n">
-        <v>42.30199505363411</v>
+        <v>42.30232621459808</v>
       </c>
       <c r="C232" t="n">
-        <v>6.046123637895509</v>
+        <v>6.046183046272517</v>
       </c>
       <c r="D232" t="n">
         <v>0</v>
@@ -3693,10 +3693,10 @@
         <v>44869</v>
       </c>
       <c r="B233" t="n">
-        <v>42.00174307719038</v>
+        <v>42.00239538844885</v>
       </c>
       <c r="C233" t="n">
-        <v>5.56517364640949</v>
+        <v>5.565288036938787</v>
       </c>
       <c r="D233" t="n">
         <v>0</v>
@@ -3707,10 +3707,10 @@
         <v>44876</v>
       </c>
       <c r="B234" t="n">
-        <v>41.99646426105742</v>
+        <v>41.99701684132638</v>
       </c>
       <c r="C234" t="n">
-        <v>5.294661386114766</v>
+        <v>5.294751469102092</v>
       </c>
       <c r="D234" t="n">
         <v>0</v>
@@ -3721,10 +3721,10 @@
         <v>44883</v>
       </c>
       <c r="B235" t="n">
-        <v>42.27831333389273</v>
+        <v>42.27881379725189</v>
       </c>
       <c r="C235" t="n">
-        <v>5.046396316326212</v>
+        <v>5.046446748477942</v>
       </c>
       <c r="D235" t="n">
         <v>0</v>
@@ -3735,10 +3735,10 @@
         <v>44890</v>
       </c>
       <c r="B236" t="n">
-        <v>42.28461592957567</v>
+        <v>42.28529101082705</v>
       </c>
       <c r="C236" t="n">
-        <v>4.573111035553294</v>
+        <v>4.573166585088436</v>
       </c>
       <c r="D236" t="n">
         <v>0</v>
@@ -3749,10 +3749,10 @@
         <v>44897</v>
       </c>
       <c r="B237" t="n">
-        <v>42.75440394618002</v>
+        <v>42.75492778275834</v>
       </c>
       <c r="C237" t="n">
-        <v>4.807103518752077</v>
+        <v>4.807193405742719</v>
       </c>
       <c r="D237" t="n">
         <v>0</v>
@@ -3763,10 +3763,10 @@
         <v>44904</v>
       </c>
       <c r="B238" t="n">
-        <v>42.74911030263536</v>
+        <v>42.74957635992778</v>
       </c>
       <c r="C238" t="n">
-        <v>4.784075382359723</v>
+        <v>4.78415144202627</v>
       </c>
       <c r="D238" t="n">
         <v>0</v>
@@ -3777,10 +3777,10 @@
         <v>44911</v>
       </c>
       <c r="B239" t="n">
-        <v>42.98200517322221</v>
+        <v>42.98244397379935</v>
       </c>
       <c r="C239" t="n">
-        <v>4.88013265678352</v>
+        <v>4.880253424427712</v>
       </c>
       <c r="D239" t="n">
         <v>0</v>
@@ -3791,10 +3791,10 @@
         <v>44918</v>
       </c>
       <c r="B240" t="n">
-        <v>42.17816899305948</v>
+        <v>42.17867082587586</v>
       </c>
       <c r="C240" t="n">
-        <v>4.064177344203827</v>
+        <v>4.064284186983318</v>
       </c>
       <c r="D240" t="n">
         <v>0</v>
@@ -3805,10 +3805,10 @@
         <v>44925</v>
       </c>
       <c r="B241" t="n">
-        <v>42.21038692904125</v>
+        <v>42.21085877502213</v>
       </c>
       <c r="C241" t="n">
-        <v>4.542577375411784</v>
+        <v>4.542633758336896</v>
       </c>
       <c r="D241" t="n">
         <v>0</v>
@@ -3819,10 +3819,10 @@
         <v>44932</v>
       </c>
       <c r="B242" t="n">
-        <v>42.54859470027912</v>
+        <v>42.54877502795344</v>
       </c>
       <c r="C242" t="n">
-        <v>5.040315909186262</v>
+        <v>5.040302381809544</v>
       </c>
       <c r="D242" t="n">
         <v>0</v>
@@ -3833,10 +3833,10 @@
         <v>44939</v>
       </c>
       <c r="B243" t="n">
-        <v>42.47136537257131</v>
+        <v>42.47149721801934</v>
       </c>
       <c r="C243" t="n">
-        <v>5.494393998313433</v>
+        <v>5.494328525974082</v>
       </c>
       <c r="D243" t="n">
         <v>0</v>
@@ -3847,10 +3847,10 @@
         <v>44946</v>
       </c>
       <c r="B244" t="n">
-        <v>42.03988411675385</v>
+        <v>42.03987687351229</v>
       </c>
       <c r="C244" t="n">
-        <v>4.281262752580885</v>
+        <v>4.281198977121496</v>
       </c>
       <c r="D244" t="n">
         <v>0</v>
@@ -3861,10 +3861,10 @@
         <v>44953</v>
       </c>
       <c r="B245" t="n">
-        <v>42.27759156112935</v>
+        <v>42.2776614078325</v>
       </c>
       <c r="C245" t="n">
-        <v>4.038906379556657</v>
+        <v>4.038860039580976</v>
       </c>
       <c r="D245" t="n">
         <v>0</v>
@@ -3875,10 +3875,10 @@
         <v>44960</v>
       </c>
       <c r="B246" t="n">
-        <v>42.3075395095613</v>
+        <v>42.30762825932936</v>
       </c>
       <c r="C246" t="n">
-        <v>4.074549687183119</v>
+        <v>4.074508542921628</v>
       </c>
       <c r="D246" t="n">
         <v>0</v>
@@ -3889,10 +3889,10 @@
         <v>44967</v>
       </c>
       <c r="B247" t="n">
-        <v>43.26815364863668</v>
+        <v>43.26827309280534</v>
       </c>
       <c r="C247" t="n">
-        <v>4.155891693437671</v>
+        <v>4.155872609816969</v>
       </c>
       <c r="D247" t="n">
         <v>0</v>
@@ -3903,10 +3903,10 @@
         <v>44974</v>
       </c>
       <c r="B248" t="n">
-        <v>42.7348279521482</v>
+        <v>42.73489876921405</v>
       </c>
       <c r="C248" t="n">
-        <v>3.223134889306198</v>
+        <v>3.223149249795536</v>
       </c>
       <c r="D248" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>44981</v>
       </c>
       <c r="B249" t="n">
-        <v>41.84816797862594</v>
+        <v>41.84806960128871</v>
       </c>
       <c r="C249" t="n">
-        <v>3.163846504212029</v>
+        <v>3.163899575392077</v>
       </c>
       <c r="D249" t="n">
         <v>0</v>
@@ -3931,10 +3931,10 @@
         <v>44988</v>
       </c>
       <c r="B250" t="n">
-        <v>41.97060110684139</v>
+        <v>41.97049491001571</v>
       </c>
       <c r="C250" t="n">
-        <v>3.498049899397068</v>
+        <v>3.498054989258966</v>
       </c>
       <c r="D250" t="n">
         <v>0</v>
@@ -3945,10 +3945,10 @@
         <v>44995</v>
       </c>
       <c r="B251" t="n">
-        <v>41.77725707315278</v>
+        <v>41.77706200780528</v>
       </c>
       <c r="C251" t="n">
-        <v>3.342332951699363</v>
+        <v>3.342292270078565</v>
       </c>
       <c r="D251" t="n">
         <v>0</v>
@@ -3959,10 +3959,10 @@
         <v>45002</v>
       </c>
       <c r="B252" t="n">
-        <v>41.74953564544689</v>
+        <v>41.74937086755033</v>
       </c>
       <c r="C252" t="n">
-        <v>3.279332716793726</v>
+        <v>3.279304624991491</v>
       </c>
       <c r="D252" t="n">
         <v>0</v>
@@ -3973,10 +3973,10 @@
         <v>45009</v>
       </c>
       <c r="B253" t="n">
-        <v>41.54909595226678</v>
+        <v>41.54889910813059</v>
       </c>
       <c r="C253" t="n">
-        <v>2.317774203304364</v>
+        <v>2.317675992991497</v>
       </c>
       <c r="D253" t="n">
         <v>0</v>
@@ -3987,10 +3987,10 @@
         <v>45016</v>
       </c>
       <c r="B254" t="n">
-        <v>41.84489954472099</v>
+        <v>41.84494569858085</v>
       </c>
       <c r="C254" t="n">
-        <v>2.541662669288875</v>
+        <v>2.541561272792554</v>
       </c>
       <c r="D254" t="n">
         <v>0</v>
@@ -4001,10 +4001,10 @@
         <v>45023</v>
       </c>
       <c r="B255" t="n">
-        <v>42.6178284379271</v>
+        <v>42.61786941865331</v>
       </c>
       <c r="C255" t="n">
-        <v>3.099587796140873</v>
+        <v>3.099565931658814</v>
       </c>
       <c r="D255" t="n">
         <v>0</v>
@@ -4015,10 +4015,10 @@
         <v>45030</v>
       </c>
       <c r="B256" t="n">
-        <v>42.80231766692117</v>
+        <v>42.80235921464963</v>
       </c>
       <c r="C256" t="n">
-        <v>2.41288455206047</v>
+        <v>2.412861297042014</v>
       </c>
       <c r="D256" t="n">
         <v>0</v>
@@ -4029,10 +4029,10 @@
         <v>45037</v>
       </c>
       <c r="B257" t="n">
-        <v>43.1864829759825</v>
+        <v>43.18646537014812</v>
       </c>
       <c r="C257" t="n">
-        <v>2.390842596763018</v>
+        <v>2.390796883484453</v>
       </c>
       <c r="D257" t="n">
         <v>0</v>
@@ -4043,10 +4043,10 @@
         <v>45044</v>
       </c>
       <c r="B258" t="n">
-        <v>45.67382956073875</v>
+        <v>45.67366589101519</v>
       </c>
       <c r="C258" t="n">
-        <v>2.333856008025007</v>
+        <v>2.333838010117225</v>
       </c>
       <c r="D258" t="n">
         <v>0</v>
@@ -4057,10 +4057,10 @@
         <v>45051</v>
       </c>
       <c r="B259" t="n">
-        <v>45.65505579208874</v>
+        <v>45.65480360807512</v>
       </c>
       <c r="C259" t="n">
-        <v>2.021680677294034</v>
+        <v>2.021639616526222</v>
       </c>
       <c r="D259" t="n">
         <v>0</v>
@@ -4071,10 +4071,10 @@
         <v>45058</v>
       </c>
       <c r="B260" t="n">
-        <v>45.62944133712856</v>
+        <v>45.62914455292887</v>
       </c>
       <c r="C260" t="n">
-        <v>2.125661260149668</v>
+        <v>2.125600474541675</v>
       </c>
       <c r="D260" t="n">
         <v>0</v>
@@ -4085,10 +4085,10 @@
         <v>45065</v>
       </c>
       <c r="B261" t="n">
-        <v>44.85274727203394</v>
+        <v>44.85263408159017</v>
       </c>
       <c r="C261" t="n">
-        <v>3.869655889761906</v>
+        <v>3.869738789865969</v>
       </c>
       <c r="D261" t="n">
         <v>0</v>
@@ -4099,10 +4099,10 @@
         <v>45072</v>
       </c>
       <c r="B262" t="n">
-        <v>45.53940212071291</v>
+        <v>45.53923863669505</v>
       </c>
       <c r="C262" t="n">
-        <v>3.84661898817124</v>
+        <v>3.846588063805842</v>
       </c>
       <c r="D262" t="n">
         <v>0</v>
@@ -4113,10 +4113,10 @@
         <v>45079</v>
       </c>
       <c r="B263" t="n">
-        <v>45.43953612569211</v>
+        <v>45.43947027962923</v>
       </c>
       <c r="C263" t="n">
-        <v>3.65311431516177</v>
+        <v>3.653092913771006</v>
       </c>
       <c r="D263" t="n">
         <v>0</v>
@@ -4127,10 +4127,10 @@
         <v>45086</v>
       </c>
       <c r="B264" t="n">
-        <v>45.87304026501339</v>
+        <v>45.87296412814734</v>
       </c>
       <c r="C264" t="n">
-        <v>3.548520883150326</v>
+        <v>3.548512395125095</v>
       </c>
       <c r="D264" t="n">
         <v>0</v>
@@ -4141,10 +4141,10 @@
         <v>45093</v>
       </c>
       <c r="B265" t="n">
-        <v>46.2076085019311</v>
+        <v>46.2074870738731</v>
       </c>
       <c r="C265" t="n">
-        <v>4.14944468462512</v>
+        <v>4.14945378165735</v>
       </c>
       <c r="D265" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>45100</v>
       </c>
       <c r="B266" t="n">
-        <v>46.48420563453715</v>
+        <v>46.48404374746608</v>
       </c>
       <c r="C266" t="n">
-        <v>3.866640272876953</v>
+        <v>3.866661334998204</v>
       </c>
       <c r="D266" t="n">
         <v>0</v>
@@ -4169,10 +4169,10 @@
         <v>45107</v>
       </c>
       <c r="B267" t="n">
-        <v>46.15700916139141</v>
+        <v>46.15679421373363</v>
       </c>
       <c r="C267" t="n">
-        <v>3.680050745168218</v>
+        <v>3.680018487508804</v>
       </c>
       <c r="D267" t="n">
         <v>0</v>
@@ -4183,10 +4183,10 @@
         <v>45114</v>
       </c>
       <c r="B268" t="n">
-        <v>46.29495670049371</v>
+        <v>46.294709497474</v>
       </c>
       <c r="C268" t="n">
-        <v>3.529560740761797</v>
+        <v>3.52951999231034</v>
       </c>
       <c r="D268" t="n">
         <v>0</v>
@@ -4197,10 +4197,10 @@
         <v>45121</v>
       </c>
       <c r="B269" t="n">
-        <v>45.88919258942413</v>
+        <v>45.88897974794526</v>
       </c>
       <c r="C269" t="n">
-        <v>3.479289514704195</v>
+        <v>3.479290912470162</v>
       </c>
       <c r="D269" t="n">
         <v>0</v>
@@ -4211,10 +4211,10 @@
         <v>45128</v>
       </c>
       <c r="B270" t="n">
-        <v>45.38111403477666</v>
+        <v>45.38101965863648</v>
       </c>
       <c r="C270" t="n">
-        <v>3.27340572473198</v>
+        <v>3.2734801670419</v>
       </c>
       <c r="D270" t="n">
         <v>0</v>
@@ -4225,10 +4225,10 @@
         <v>45135</v>
       </c>
       <c r="B271" t="n">
-        <v>45.32202781141411</v>
+        <v>45.32195525821382</v>
       </c>
       <c r="C271" t="n">
-        <v>3.316998175214492</v>
+        <v>3.317095831206763</v>
       </c>
       <c r="D271" t="n">
         <v>0</v>
@@ -4239,10 +4239,10 @@
         <v>45142</v>
       </c>
       <c r="B272" t="n">
-        <v>45.68030644308136</v>
+        <v>45.68018970064964</v>
       </c>
       <c r="C272" t="n">
-        <v>3.19999371461194</v>
+        <v>3.200122393647568</v>
       </c>
       <c r="D272" t="n">
         <v>0</v>
@@ -4253,10 +4253,10 @@
         <v>45149</v>
       </c>
       <c r="B273" t="n">
-        <v>44.23430134449429</v>
+        <v>44.23419187948976</v>
       </c>
       <c r="C273" t="n">
-        <v>2.450291546600829</v>
+        <v>2.450389420487828</v>
       </c>
       <c r="D273" t="n">
         <v>0</v>
@@ -4267,10 +4267,10 @@
         <v>45156</v>
       </c>
       <c r="B274" t="n">
-        <v>43.80275088249756</v>
+        <v>43.80265101459094</v>
       </c>
       <c r="C274" t="n">
-        <v>2.316287999985308</v>
+        <v>2.316316291476209</v>
       </c>
       <c r="D274" t="n">
         <v>0</v>
@@ -4281,10 +4281,10 @@
         <v>45163</v>
       </c>
       <c r="B275" t="n">
-        <v>44.25196738676657</v>
+        <v>44.25203786341626</v>
       </c>
       <c r="C275" t="n">
-        <v>2.559879751511998</v>
+        <v>2.559927371507976</v>
       </c>
       <c r="D275" t="n">
         <v>0</v>
@@ -4295,10 +4295,10 @@
         <v>45170</v>
       </c>
       <c r="B276" t="n">
-        <v>44.29653842734864</v>
+        <v>44.29639879718491</v>
       </c>
       <c r="C276" t="n">
-        <v>2.157504242171897</v>
+        <v>2.157565488662831</v>
       </c>
       <c r="D276" t="n">
         <v>0</v>
@@ -4309,10 +4309,10 @@
         <v>45177</v>
       </c>
       <c r="B277" t="n">
-        <v>44.26750430931776</v>
+        <v>44.26745777594528</v>
       </c>
       <c r="C277" t="n">
-        <v>2.41304520092898</v>
+        <v>2.413088311183365</v>
       </c>
       <c r="D277" t="n">
         <v>0</v>
@@ -4323,10 +4323,10 @@
         <v>45184</v>
       </c>
       <c r="B278" t="n">
-        <v>42.78070560589332</v>
+        <v>42.78085219013035</v>
       </c>
       <c r="C278" t="n">
-        <v>1.600066683808909</v>
+        <v>1.600001889437241</v>
       </c>
       <c r="D278" t="n">
         <v>0</v>
@@ -4337,10 +4337,10 @@
         <v>45191</v>
       </c>
       <c r="B279" t="n">
-        <v>42.77568979462695</v>
+        <v>42.77575304954746</v>
       </c>
       <c r="C279" t="n">
-        <v>1.433224992853192</v>
+        <v>1.433223242937959</v>
       </c>
       <c r="D279" t="n">
         <v>0</v>
@@ -4351,10 +4351,10 @@
         <v>45198</v>
       </c>
       <c r="B280" t="n">
-        <v>42.79615701086137</v>
+        <v>42.7960229587969</v>
       </c>
       <c r="C280" t="n">
-        <v>1.608276332342834</v>
+        <v>1.608272000996635</v>
       </c>
       <c r="D280" t="n">
         <v>0</v>
@@ -4365,10 +4365,10 @@
         <v>45205</v>
       </c>
       <c r="B281" t="n">
-        <v>42.89037166265846</v>
+        <v>42.89033746360929</v>
       </c>
       <c r="C281" t="n">
-        <v>1.560552074492568</v>
+        <v>1.560548380006221</v>
       </c>
       <c r="D281" t="n">
         <v>0</v>
@@ -4379,10 +4379,10 @@
         <v>45212</v>
       </c>
       <c r="B282" t="n">
-        <v>43.32445808158824</v>
+        <v>43.32426804853966</v>
       </c>
       <c r="C282" t="n">
-        <v>1.455630253480046</v>
+        <v>1.455599053640696</v>
       </c>
       <c r="D282" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>45219</v>
       </c>
       <c r="B283" t="n">
-        <v>43.91000433764631</v>
+        <v>43.90978941737979</v>
       </c>
       <c r="C283" t="n">
-        <v>1.654583625619132</v>
+        <v>1.65454593887044</v>
       </c>
       <c r="D283" t="n">
         <v>0</v>
@@ -4407,10 +4407,10 @@
         <v>45226</v>
       </c>
       <c r="B284" t="n">
-        <v>42.11511354061918</v>
+        <v>42.11491183270771</v>
       </c>
       <c r="C284" t="n">
-        <v>1.242867266320942</v>
+        <v>1.242845038176279</v>
       </c>
       <c r="D284" t="n">
         <v>0</v>
@@ -4421,10 +4421,10 @@
         <v>45233</v>
       </c>
       <c r="B285" t="n">
-        <v>42.47902686008546</v>
+        <v>42.47865732500543</v>
       </c>
       <c r="C285" t="n">
-        <v>1.331843246094399</v>
+        <v>1.331826047227619</v>
       </c>
       <c r="D285" t="n">
         <v>0</v>
@@ -4435,10 +4435,10 @@
         <v>45240</v>
       </c>
       <c r="B286" t="n">
-        <v>42.04587872476367</v>
+        <v>42.04552616372981</v>
       </c>
       <c r="C286" t="n">
-        <v>1.395858617150526</v>
+        <v>1.395868009243358</v>
       </c>
       <c r="D286" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>45247</v>
       </c>
       <c r="B287" t="n">
-        <v>40.40266005827002</v>
+        <v>40.40260750295141</v>
       </c>
       <c r="C287" t="n">
-        <v>1.640169453899661</v>
+        <v>1.640156588090561</v>
       </c>
       <c r="D287" t="n">
         <v>0</v>
@@ -4463,10 +4463,10 @@
         <v>45254</v>
       </c>
       <c r="B288" t="n">
-        <v>41.12632217213265</v>
+        <v>41.12635789372693</v>
       </c>
       <c r="C288" t="n">
-        <v>2.233552144484015</v>
+        <v>2.233538809038504</v>
       </c>
       <c r="D288" t="n">
         <v>0</v>
@@ -4477,10 +4477,10 @@
         <v>45261</v>
       </c>
       <c r="B289" t="n">
-        <v>41.56933904633795</v>
+        <v>41.56940169346981</v>
       </c>
       <c r="C289" t="n">
-        <v>2.3320007129241</v>
+        <v>2.331961619248363</v>
       </c>
       <c r="D289" t="n">
         <v>0</v>
@@ -4491,10 +4491,10 @@
         <v>45268</v>
       </c>
       <c r="B290" t="n">
-        <v>41.18647356684468</v>
+        <v>41.18658531346094</v>
       </c>
       <c r="C290" t="n">
-        <v>2.120546551407114</v>
+        <v>2.120445574481684</v>
       </c>
       <c r="D290" t="n">
         <v>0</v>
@@ -4505,10 +4505,10 @@
         <v>45275</v>
       </c>
       <c r="B291" t="n">
-        <v>40.79772783730501</v>
+        <v>40.79787819693296</v>
       </c>
       <c r="C291" t="n">
-        <v>2.09399923328699</v>
+        <v>2.093908361750457</v>
       </c>
       <c r="D291" t="n">
         <v>0</v>
@@ -4519,10 +4519,10 @@
         <v>45282</v>
       </c>
       <c r="B292" t="n">
-        <v>42.0119546224203</v>
+        <v>42.01213896921676</v>
       </c>
       <c r="C292" t="n">
-        <v>2.621047365442861</v>
+        <v>2.620975183762216</v>
       </c>
       <c r="D292" t="n">
         <v>0</v>
@@ -4533,10 +4533,10 @@
         <v>45289</v>
       </c>
       <c r="B293" t="n">
-        <v>42.63756736425032</v>
+        <v>42.6375902734434</v>
       </c>
       <c r="C293" t="n">
-        <v>3.098495262723869</v>
+        <v>3.09840176436655</v>
       </c>
       <c r="D293" t="n">
         <v>0</v>
@@ -4547,10 +4547,10 @@
         <v>45296</v>
       </c>
       <c r="B294" t="n">
-        <v>41.86200360943597</v>
+        <v>41.86212919163922</v>
       </c>
       <c r="C294" t="n">
-        <v>2.94850801592772</v>
+        <v>2.94830958649357</v>
       </c>
       <c r="D294" t="n">
         <v>0</v>
@@ -4561,10 +4561,10 @@
         <v>45303</v>
       </c>
       <c r="B295" t="n">
-        <v>41.19463764092071</v>
+        <v>41.19432622204437</v>
       </c>
       <c r="C295" t="n">
-        <v>2.77608495353196</v>
+        <v>2.775936179598136</v>
       </c>
       <c r="D295" t="n">
         <v>0</v>
@@ -4575,10 +4575,10 @@
         <v>45310</v>
       </c>
       <c r="B296" t="n">
-        <v>40.39999240025376</v>
+        <v>40.39934428491393</v>
       </c>
       <c r="C296" t="n">
-        <v>2.296858219094319</v>
+        <v>2.296743247635284</v>
       </c>
       <c r="D296" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>45317</v>
       </c>
       <c r="B297" t="n">
-        <v>40.08951428084585</v>
+        <v>40.0888916435706</v>
       </c>
       <c r="C297" t="n">
-        <v>2.102641149082379</v>
+        <v>2.102561191738447</v>
       </c>
       <c r="D297" t="n">
         <v>0</v>
@@ -4603,10 +4603,10 @@
         <v>45324</v>
       </c>
       <c r="B298" t="n">
-        <v>40.55528128037361</v>
+        <v>40.55452244905271</v>
       </c>
       <c r="C298" t="n">
-        <v>2.064939979918634</v>
+        <v>2.06483867810149</v>
       </c>
       <c r="D298" t="n">
         <v>0</v>
@@ -4617,10 +4617,10 @@
         <v>45331</v>
       </c>
       <c r="B299" t="n">
-        <v>40.19950953645392</v>
+        <v>40.19910150049324</v>
       </c>
       <c r="C299" t="n">
-        <v>1.947347986019999</v>
+        <v>1.947159392321354</v>
       </c>
       <c r="D299" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>45338</v>
       </c>
       <c r="B300" t="n">
-        <v>46.6313979712751</v>
+        <v>46.63085767587651</v>
       </c>
       <c r="C300" t="n">
-        <v>6.284434363823882</v>
+        <v>6.284312238611389</v>
       </c>
       <c r="D300" t="n">
         <v>0</v>
@@ -4645,10 +4645,10 @@
         <v>45345</v>
       </c>
       <c r="B301" t="n">
-        <v>44.60930290126201</v>
+        <v>44.60865877693788</v>
       </c>
       <c r="C301" t="n">
-        <v>5.553155535774547</v>
+        <v>5.553241268827043</v>
       </c>
       <c r="D301" t="n">
         <v>0</v>
@@ -4659,10 +4659,10 @@
         <v>45352</v>
       </c>
       <c r="B302" t="n">
-        <v>44.04776925341176</v>
+        <v>44.04722915960918</v>
       </c>
       <c r="C302" t="n">
-        <v>3.830150258131949</v>
+        <v>3.830264980198515</v>
       </c>
       <c r="D302" t="n">
         <v>0</v>
@@ -4673,10 +4673,10 @@
         <v>45359</v>
       </c>
       <c r="B303" t="n">
-        <v>44.14195093893945</v>
+        <v>44.14142798196585</v>
       </c>
       <c r="C303" t="n">
-        <v>3.933999342323568</v>
+        <v>3.934185408422909</v>
       </c>
       <c r="D303" t="n">
         <v>0</v>
@@ -4687,10 +4687,10 @@
         <v>45366</v>
       </c>
       <c r="B304" t="n">
-        <v>44.02534055099389</v>
+        <v>44.02489208198023</v>
       </c>
       <c r="C304" t="n">
-        <v>3.182590141976805</v>
+        <v>3.182709600483966</v>
       </c>
       <c r="D304" t="n">
         <v>0</v>
@@ -4701,10 +4701,10 @@
         <v>45373</v>
       </c>
       <c r="B305" t="n">
-        <v>46.69094796869501</v>
+        <v>46.69045293568055</v>
       </c>
       <c r="C305" t="n">
-        <v>5.080960722443591</v>
+        <v>5.081303092179391</v>
       </c>
       <c r="D305" t="n">
         <v>0</v>
@@ -4715,10 +4715,10 @@
         <v>45380</v>
       </c>
       <c r="B306" t="n">
-        <v>46.69414378576463</v>
+        <v>46.69360966547973</v>
       </c>
       <c r="C306" t="n">
-        <v>5.384327992577858</v>
+        <v>5.384695604684671</v>
       </c>
       <c r="D306" t="n">
         <v>0</v>
@@ -4729,10 +4729,10 @@
         <v>45387</v>
       </c>
       <c r="B307" t="n">
-        <v>47.68059755067329</v>
+        <v>47.67982633166462</v>
       </c>
       <c r="C307" t="n">
-        <v>5.79821838869358</v>
+        <v>5.79864791244048</v>
       </c>
       <c r="D307" t="n">
         <v>0</v>
@@ -4743,10 +4743,10 @@
         <v>45394</v>
       </c>
       <c r="B308" t="n">
-        <v>48.15769985611621</v>
+        <v>48.1568895063</v>
       </c>
       <c r="C308" t="n">
-        <v>6.444275000321908</v>
+        <v>6.444764185412319</v>
       </c>
       <c r="D308" t="n">
         <v>0</v>
@@ -4757,10 +4757,10 @@
         <v>45401</v>
       </c>
       <c r="B309" t="n">
-        <v>47.79780154733279</v>
+        <v>47.79711932646774</v>
       </c>
       <c r="C309" t="n">
-        <v>6.651233411807074</v>
+        <v>6.651849450599925</v>
       </c>
       <c r="D309" t="n">
         <v>0</v>
@@ -4771,10 +4771,10 @@
         <v>45408</v>
       </c>
       <c r="B310" t="n">
-        <v>48.38127402268464</v>
+        <v>48.38065468951697</v>
       </c>
       <c r="C310" t="n">
-        <v>7.892768598145914</v>
+        <v>7.893321635132364</v>
       </c>
       <c r="D310" t="n">
         <v>0</v>
@@ -4785,10 +4785,10 @@
         <v>45415</v>
       </c>
       <c r="B311" t="n">
-        <v>48.99191718048451</v>
+        <v>48.99133630322263</v>
       </c>
       <c r="C311" t="n">
-        <v>8.68256323523851</v>
+        <v>8.683052881839993</v>
       </c>
       <c r="D311" t="n">
         <v>0</v>
@@ -4799,10 +4799,10 @@
         <v>45422</v>
       </c>
       <c r="B312" t="n">
-        <v>48.66516249723092</v>
+        <v>48.66486090583955</v>
       </c>
       <c r="C312" t="n">
-        <v>9.128938086761869</v>
+        <v>9.129440928279902</v>
       </c>
       <c r="D312" t="n">
         <v>0</v>
@@ -4813,10 +4813,10 @@
         <v>45429</v>
       </c>
       <c r="B313" t="n">
-        <v>48.24537120734877</v>
+        <v>48.24508916114465</v>
       </c>
       <c r="C313" t="n">
-        <v>8.770184058392511</v>
+        <v>8.770608752577449</v>
       </c>
       <c r="D313" t="n">
         <v>0</v>
@@ -4827,10 +4827,10 @@
         <v>45436</v>
       </c>
       <c r="B314" t="n">
-        <v>48.6538187358578</v>
+        <v>48.65356753846071</v>
       </c>
       <c r="C314" t="n">
-        <v>9.146230108594018</v>
+        <v>9.146730297382479</v>
       </c>
       <c r="D314" t="n">
         <v>0</v>
@@ -4841,10 +4841,10 @@
         <v>45443</v>
       </c>
       <c r="B315" t="n">
-        <v>48.41710965585371</v>
+        <v>48.41676656337011</v>
       </c>
       <c r="C315" t="n">
-        <v>8.51263854346073</v>
+        <v>8.512924380148716</v>
       </c>
       <c r="D315" t="n">
         <v>0</v>
@@ -4855,10 +4855,10 @@
         <v>45450</v>
       </c>
       <c r="B316" t="n">
-        <v>49.2361295987721</v>
+        <v>49.23584042425813</v>
       </c>
       <c r="C316" t="n">
-        <v>9.332158242240945</v>
+        <v>9.33242532640749</v>
       </c>
       <c r="D316" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>45457</v>
       </c>
       <c r="B317" t="n">
-        <v>48.93226389121983</v>
+        <v>48.93196651223482</v>
       </c>
       <c r="C317" t="n">
-        <v>8.916866202242369</v>
+        <v>8.917112512015697</v>
       </c>
       <c r="D317" t="n">
         <v>0</v>
@@ -4883,10 +4883,10 @@
         <v>45464</v>
       </c>
       <c r="B318" t="n">
-        <v>48.91576484499617</v>
+        <v>48.91572143670194</v>
       </c>
       <c r="C318" t="n">
-        <v>9.013871701007005</v>
+        <v>9.014066176419256</v>
       </c>
       <c r="D318" t="n">
         <v>0</v>
@@ -4897,10 +4897,10 @@
         <v>45471</v>
       </c>
       <c r="B319" t="n">
-        <v>48.77038864302554</v>
+        <v>48.77036710117896</v>
       </c>
       <c r="C319" t="n">
-        <v>8.036435463081412</v>
+        <v>8.036548432681659</v>
       </c>
       <c r="D319" t="n">
         <v>0</v>
@@ -4911,10 +4911,10 @@
         <v>45478</v>
       </c>
       <c r="B320" t="n">
-        <v>49.02824306154133</v>
+        <v>49.02824375412691</v>
       </c>
       <c r="C320" t="n">
-        <v>8.636821834680614</v>
+        <v>8.636946029310598</v>
       </c>
       <c r="D320" t="n">
         <v>0</v>
@@ -4925,10 +4925,10 @@
         <v>45485</v>
       </c>
       <c r="B321" t="n">
-        <v>49.49776723453981</v>
+        <v>49.49776225470214</v>
       </c>
       <c r="C321" t="n">
-        <v>8.880380297817057</v>
+        <v>8.880601729380997</v>
       </c>
       <c r="D321" t="n">
         <v>0</v>
@@ -4939,10 +4939,10 @@
         <v>45492</v>
       </c>
       <c r="B322" t="n">
-        <v>50.1632037412671</v>
+        <v>50.16315572519375</v>
       </c>
       <c r="C322" t="n">
-        <v>9.28255120816595</v>
+        <v>9.282692103015048</v>
       </c>
       <c r="D322" t="n">
         <v>0</v>
@@ -4953,10 +4953,10 @@
         <v>45499</v>
       </c>
       <c r="B323" t="n">
-        <v>50.27996617248137</v>
+        <v>50.27993245838272</v>
       </c>
       <c r="C323" t="n">
-        <v>9.559387404937533</v>
+        <v>9.559531595304477</v>
       </c>
       <c r="D323" t="n">
         <v>0</v>
@@ -4967,10 +4967,10 @@
         <v>45506</v>
       </c>
       <c r="B324" t="n">
-        <v>51.35228683084703</v>
+        <v>51.35235785507199</v>
       </c>
       <c r="C324" t="n">
-        <v>9.476500858993145</v>
+        <v>9.476715215800645</v>
       </c>
       <c r="D324" t="n">
         <v>0</v>
@@ -4981,10 +4981,10 @@
         <v>45513</v>
       </c>
       <c r="B325" t="n">
-        <v>51.17691968712659</v>
+        <v>51.17688520425691</v>
       </c>
       <c r="C325" t="n">
-        <v>9.187582121611836</v>
+        <v>9.187800431701076</v>
       </c>
       <c r="D325" t="n">
         <v>0</v>
@@ -4995,10 +4995,10 @@
         <v>45520</v>
       </c>
       <c r="B326" t="n">
-        <v>51.13547412329899</v>
+        <v>51.13549109636266</v>
       </c>
       <c r="C326" t="n">
-        <v>8.815920392513352</v>
+        <v>8.816166816664303</v>
       </c>
       <c r="D326" t="n">
         <v>0</v>
@@ -5009,10 +5009,10 @@
         <v>45527</v>
       </c>
       <c r="B327" t="n">
-        <v>49.8173260381295</v>
+        <v>49.81714431244333</v>
       </c>
       <c r="C327" t="n">
-        <v>8.444662178184588</v>
+        <v>8.44475122035842</v>
       </c>
       <c r="D327" t="n">
         <v>0</v>
@@ -5023,10 +5023,10 @@
         <v>45534</v>
       </c>
       <c r="B328" t="n">
-        <v>49.62173937260433</v>
+        <v>49.62185616196148</v>
       </c>
       <c r="C328" t="n">
-        <v>8.710443408975086</v>
+        <v>8.710692602881915</v>
       </c>
       <c r="D328" t="n">
         <v>0</v>
@@ -5037,10 +5037,10 @@
         <v>45541</v>
       </c>
       <c r="B329" t="n">
-        <v>48.78925377608198</v>
+        <v>48.7892403888119</v>
       </c>
       <c r="C329" t="n">
-        <v>8.413917673295503</v>
+        <v>8.414133869053549</v>
       </c>
       <c r="D329" t="n">
         <v>0</v>
@@ -5051,10 +5051,10 @@
         <v>45548</v>
       </c>
       <c r="B330" t="n">
-        <v>50.64696034999282</v>
+        <v>50.64735612468245</v>
       </c>
       <c r="C330" t="n">
-        <v>10.30525661972675</v>
+        <v>10.30540803165764</v>
       </c>
       <c r="D330" t="n">
         <v>0</v>
@@ -5065,10 +5065,10 @@
         <v>45555</v>
       </c>
       <c r="B331" t="n">
-        <v>50.51766138599336</v>
+        <v>50.51799851951055</v>
       </c>
       <c r="C331" t="n">
-        <v>10.0862470975876</v>
+        <v>10.08645944824261</v>
       </c>
       <c r="D331" t="n">
         <v>0</v>
@@ -5079,10 +5079,10 @@
         <v>45562</v>
       </c>
       <c r="B332" t="n">
-        <v>51.08300740884712</v>
+        <v>51.08320945950641</v>
       </c>
       <c r="C332" t="n">
-        <v>10.973035684392</v>
+        <v>10.97333596512819</v>
       </c>
       <c r="D332" t="n">
         <v>0</v>
@@ -5093,10 +5093,10 @@
         <v>45569</v>
       </c>
       <c r="B333" t="n">
-        <v>51.09390926544558</v>
+        <v>51.0941610160197</v>
       </c>
       <c r="C333" t="n">
-        <v>11.03070591846201</v>
+        <v>11.03095457510493</v>
       </c>
       <c r="D333" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>45576</v>
       </c>
       <c r="B334" t="n">
-        <v>50.80602477281644</v>
+        <v>50.80625239789995</v>
       </c>
       <c r="C334" t="n">
-        <v>10.97071692924441</v>
+        <v>10.97095193845906</v>
       </c>
       <c r="D334" t="n">
         <v>0</v>
@@ -5121,10 +5121,10 @@
         <v>45583</v>
       </c>
       <c r="B335" t="n">
-        <v>51.05207355341341</v>
+        <v>51.05214004925254</v>
       </c>
       <c r="C335" t="n">
-        <v>9.768103929020658</v>
+        <v>9.768211101312344</v>
       </c>
       <c r="D335" t="n">
         <v>0</v>
@@ -5135,10 +5135,10 @@
         <v>45590</v>
       </c>
       <c r="B336" t="n">
-        <v>51.32517553889355</v>
+        <v>51.32575447627008</v>
       </c>
       <c r="C336" t="n">
-        <v>8.126063800696359</v>
+        <v>8.126162067667021</v>
       </c>
       <c r="D336" t="n">
         <v>0</v>
@@ -5149,10 +5149,10 @@
         <v>45597</v>
       </c>
       <c r="B337" t="n">
-        <v>51.28931870143973</v>
+        <v>51.28981261576786</v>
       </c>
       <c r="C337" t="n">
-        <v>7.176213632563901</v>
+        <v>7.176289112814914</v>
       </c>
       <c r="D337" t="n">
         <v>0</v>
@@ -5163,10 +5163,10 @@
         <v>45604</v>
       </c>
       <c r="B338" t="n">
-        <v>51.88679693249792</v>
+        <v>51.88724867478436</v>
       </c>
       <c r="C338" t="n">
-        <v>7.349688902715835</v>
+        <v>7.349771355962506</v>
       </c>
       <c r="D338" t="n">
         <v>0</v>
@@ -5177,10 +5177,10 @@
         <v>45611</v>
       </c>
       <c r="B339" t="n">
-        <v>52.61930628675113</v>
+        <v>52.61981037643444</v>
       </c>
       <c r="C339" t="n">
-        <v>7.948276785646372</v>
+        <v>7.948385397525079</v>
       </c>
       <c r="D339" t="n">
         <v>0</v>
@@ -5191,10 +5191,10 @@
         <v>45618</v>
       </c>
       <c r="B340" t="n">
-        <v>52.26114719137183</v>
+        <v>52.26166986965671</v>
       </c>
       <c r="C340" t="n">
-        <v>7.904159309398268</v>
+        <v>7.904277754433613</v>
       </c>
       <c r="D340" t="n">
         <v>0</v>
@@ -5205,10 +5205,10 @@
         <v>45625</v>
       </c>
       <c r="B341" t="n">
-        <v>52.29136887913275</v>
+        <v>52.29199869918524</v>
       </c>
       <c r="C341" t="n">
-        <v>7.898350295564051</v>
+        <v>7.898469610282536</v>
       </c>
       <c r="D341" t="n">
         <v>0</v>
@@ -5219,10 +5219,10 @@
         <v>45632</v>
       </c>
       <c r="B342" t="n">
-        <v>52.32700500385514</v>
+        <v>52.32761887937897</v>
       </c>
       <c r="C342" t="n">
-        <v>7.762906479720745</v>
+        <v>7.762999782160782</v>
       </c>
       <c r="D342" t="n">
         <v>0</v>
@@ -5233,10 +5233,10 @@
         <v>45639</v>
       </c>
       <c r="B343" t="n">
-        <v>51.88342289923019</v>
+        <v>51.88399491041667</v>
       </c>
       <c r="C343" t="n">
-        <v>7.840619272748532</v>
+        <v>7.840706691291209</v>
       </c>
       <c r="D343" t="n">
         <v>0</v>
@@ -5247,10 +5247,10 @@
         <v>45646</v>
       </c>
       <c r="B344" t="n">
-        <v>52.20314803151567</v>
+        <v>52.20378416280028</v>
       </c>
       <c r="C344" t="n">
-        <v>7.569719248636264</v>
+        <v>7.569817317958667</v>
       </c>
       <c r="D344" t="n">
         <v>0</v>
@@ -5261,10 +5261,10 @@
         <v>45653</v>
       </c>
       <c r="B345" t="n">
-        <v>53.1143303166666</v>
+        <v>53.11503365282314</v>
       </c>
       <c r="C345" t="n">
-        <v>7.601761434840141</v>
+        <v>7.601865730198933</v>
       </c>
       <c r="D345" t="n">
         <v>0</v>
@@ -5275,10 +5275,10 @@
         <v>45660</v>
       </c>
       <c r="B346" t="n">
-        <v>53.36978993239308</v>
+        <v>53.37059918633443</v>
       </c>
       <c r="C346" t="n">
-        <v>7.262834414221199</v>
+        <v>7.262957482184405</v>
       </c>
       <c r="D346" t="n">
         <v>0</v>
@@ -5289,10 +5289,10 @@
         <v>45667</v>
       </c>
       <c r="B347" t="n">
-        <v>53.85270623242349</v>
+        <v>53.85373825463236</v>
       </c>
       <c r="C347" t="n">
-        <v>7.935285927377764</v>
+        <v>7.9355455597843</v>
       </c>
       <c r="D347" t="n">
         <v>0</v>
@@ -5303,10 +5303,10 @@
         <v>45674</v>
       </c>
       <c r="B348" t="n">
-        <v>54.16891014107043</v>
+        <v>54.16999727647271</v>
       </c>
       <c r="C348" t="n">
-        <v>8.157009303208296</v>
+        <v>8.157269974971271</v>
       </c>
       <c r="D348" t="n">
         <v>0</v>
@@ -5317,10 +5317,10 @@
         <v>45681</v>
       </c>
       <c r="B349" t="n">
-        <v>54.5567512230887</v>
+        <v>54.55807648837421</v>
       </c>
       <c r="C349" t="n">
-        <v>8.87060204835138</v>
+        <v>8.870830507940331</v>
       </c>
       <c r="D349" t="n">
         <v>0</v>
@@ -5331,10 +5331,10 @@
         <v>45688</v>
       </c>
       <c r="B350" t="n">
-        <v>55.02457434941198</v>
+        <v>55.0255238019496</v>
       </c>
       <c r="C350" t="n">
-        <v>8.818916767754175</v>
+        <v>8.81927649867186</v>
       </c>
       <c r="D350" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>45695</v>
       </c>
       <c r="B351" t="n">
-        <v>52.1518989806701</v>
+        <v>52.15276543132126</v>
       </c>
       <c r="C351" t="n">
-        <v>6.339025708338859</v>
+        <v>6.338892825748892</v>
       </c>
       <c r="D351" t="n">
         <v>0</v>
@@ -5359,10 +5359,10 @@
         <v>45702</v>
       </c>
       <c r="B352" t="n">
-        <v>53.46396414691981</v>
+        <v>53.46539259330563</v>
       </c>
       <c r="C352" t="n">
-        <v>6.643330759475989</v>
+        <v>6.64309231752127</v>
       </c>
       <c r="D352" t="n">
         <v>0</v>
@@ -5373,10 +5373,10 @@
         <v>45709</v>
       </c>
       <c r="B353" t="n">
-        <v>52.89258076162256</v>
+        <v>52.89396470901855</v>
       </c>
       <c r="C353" t="n">
-        <v>6.955384414878321</v>
+        <v>6.955174099626484</v>
       </c>
       <c r="D353" t="n">
         <v>0</v>
@@ -5387,10 +5387,10 @@
         <v>45716</v>
       </c>
       <c r="B354" t="n">
-        <v>53.33164773624622</v>
+        <v>53.33313178583774</v>
       </c>
       <c r="C354" t="n">
-        <v>6.784610583631659</v>
+        <v>6.784376242377263</v>
       </c>
       <c r="D354" t="n">
         <v>0</v>
@@ -5401,10 +5401,10 @@
         <v>45723</v>
       </c>
       <c r="B355" t="n">
-        <v>53.82901968739505</v>
+        <v>53.83058166380598</v>
       </c>
       <c r="C355" t="n">
-        <v>7.337718279972826</v>
+        <v>7.337393282627799</v>
       </c>
       <c r="D355" t="n">
         <v>0</v>
@@ -5415,10 +5415,10 @@
         <v>45730</v>
       </c>
       <c r="B356" t="n">
-        <v>51.25230144315697</v>
+        <v>51.25373013295917</v>
       </c>
       <c r="C356" t="n">
-        <v>5.265643237018086</v>
+        <v>5.265712745785519</v>
       </c>
       <c r="D356" t="n">
         <v>0</v>
@@ -5429,10 +5429,10 @@
         <v>45737</v>
       </c>
       <c r="B357" t="n">
-        <v>51.33034821411346</v>
+        <v>51.33203572632763</v>
       </c>
       <c r="C357" t="n">
-        <v>3.143559775376181</v>
+        <v>3.143567475064223</v>
       </c>
       <c r="D357" t="n">
         <v>0</v>
@@ -5443,10 +5443,10 @@
         <v>45744</v>
       </c>
       <c r="B358" t="n">
-        <v>51.02647382766307</v>
+        <v>51.02811046532725</v>
       </c>
       <c r="C358" t="n">
-        <v>2.970734954953834</v>
+        <v>2.970775238049439</v>
       </c>
       <c r="D358" t="n">
         <v>0</v>
@@ -5457,10 +5457,10 @@
         <v>45751</v>
       </c>
       <c r="B359" t="n">
-        <v>50.54756577087863</v>
+        <v>50.54922492965142</v>
       </c>
       <c r="C359" t="n">
-        <v>2.724845235514467</v>
+        <v>2.724871813874147</v>
       </c>
       <c r="D359" t="n">
         <v>0</v>
@@ -5471,10 +5471,10 @@
         <v>45758</v>
       </c>
       <c r="B360" t="n">
-        <v>50.7563870825247</v>
+        <v>50.75795418177012</v>
       </c>
       <c r="C360" t="n">
-        <v>2.606536734940065</v>
+        <v>2.60642397058317</v>
       </c>
       <c r="D360" t="n">
         <v>0</v>
@@ -5485,10 +5485,10 @@
         <v>45765</v>
       </c>
       <c r="B361" t="n">
-        <v>50.88507770420449</v>
+        <v>50.88634932688904</v>
       </c>
       <c r="C361" t="n">
-        <v>2.661160546910831</v>
+        <v>2.661089375230564</v>
       </c>
       <c r="D361" t="n">
         <v>0</v>
@@ -5499,10 +5499,10 @@
         <v>45772</v>
       </c>
       <c r="B362" t="n">
-        <v>52.50625647218886</v>
+        <v>52.50728263240956</v>
       </c>
       <c r="C362" t="n">
-        <v>4.561558796551725</v>
+        <v>4.561391917010098</v>
       </c>
       <c r="D362" t="n">
         <v>0</v>
@@ -5513,10 +5513,10 @@
         <v>45779</v>
       </c>
       <c r="B363" t="n">
-        <v>51.13523203491935</v>
+        <v>51.13624715591921</v>
       </c>
       <c r="C363" t="n">
-        <v>4.813338156106953</v>
+        <v>4.813107276815328</v>
       </c>
       <c r="D363" t="n">
         <v>0</v>
@@ -5527,10 +5527,10 @@
         <v>45786</v>
       </c>
       <c r="B364" t="n">
-        <v>51.74621436649556</v>
+        <v>51.74718932312701</v>
       </c>
       <c r="C364" t="n">
-        <v>5.436945203232077</v>
+        <v>5.436787111316846</v>
       </c>
       <c r="D364" t="n">
         <v>0</v>
@@ -5541,10 +5541,10 @@
         <v>45793</v>
       </c>
       <c r="B365" t="n">
-        <v>51.64471833419379</v>
+        <v>51.64581757653783</v>
       </c>
       <c r="C365" t="n">
-        <v>5.338416129475949</v>
+        <v>5.338241480218293</v>
       </c>
       <c r="D365" t="n">
         <v>0</v>
@@ -5555,10 +5555,10 @@
         <v>45800</v>
       </c>
       <c r="B366" t="n">
-        <v>51.95706358198212</v>
+        <v>51.95817568328309</v>
       </c>
       <c r="C366" t="n">
-        <v>6.464276811743828</v>
+        <v>6.464078430644501</v>
       </c>
       <c r="D366" t="n">
         <v>0</v>
@@ -5569,10 +5569,10 @@
         <v>45807</v>
       </c>
       <c r="B367" t="n">
-        <v>52.45216252249531</v>
+        <v>52.45300210206849</v>
       </c>
       <c r="C367" t="n">
-        <v>5.806800558849621</v>
+        <v>5.806608882731171</v>
       </c>
       <c r="D367" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>45814</v>
       </c>
       <c r="B368" t="n">
-        <v>53.53401177674692</v>
+        <v>53.53504595468252</v>
       </c>
       <c r="C368" t="n">
-        <v>6.55114706589105</v>
+        <v>6.550863880021828</v>
       </c>
       <c r="D368" t="n">
         <v>0</v>
@@ -5597,10 +5597,10 @@
         <v>45821</v>
       </c>
       <c r="B369" t="n">
-        <v>53.52211880232736</v>
+        <v>53.52311974463336</v>
       </c>
       <c r="C369" t="n">
-        <v>6.331475942331166</v>
+        <v>6.331208609682024</v>
       </c>
       <c r="D369" t="n">
         <v>0</v>
@@ -5611,10 +5611,10 @@
         <v>45828</v>
       </c>
       <c r="B370" t="n">
-        <v>53.15745611159932</v>
+        <v>53.15837879676144</v>
       </c>
       <c r="C370" t="n">
-        <v>6.431697398692844</v>
+        <v>6.43138928647878</v>
       </c>
       <c r="D370" t="n">
         <v>0</v>
@@ -5625,10 +5625,10 @@
         <v>45835</v>
       </c>
       <c r="B371" t="n">
-        <v>53.62586097385103</v>
+        <v>53.62689226655666</v>
       </c>
       <c r="C371" t="n">
-        <v>6.282167503997291</v>
+        <v>6.281899085878613</v>
       </c>
       <c r="D371" t="n">
         <v>0</v>
@@ -5639,10 +5639,10 @@
         <v>45842</v>
       </c>
       <c r="B372" t="n">
-        <v>53.71312323553929</v>
+        <v>53.71390964646638</v>
       </c>
       <c r="C372" t="n">
-        <v>6.262142484731839</v>
+        <v>6.261863623171917</v>
       </c>
       <c r="D372" t="n">
         <v>0</v>
@@ -5653,10 +5653,10 @@
         <v>45849</v>
       </c>
       <c r="B373" t="n">
-        <v>53.53330259809912</v>
+        <v>53.53406517280592</v>
       </c>
       <c r="C373" t="n">
-        <v>6.323859671776223</v>
+        <v>6.323585025822842</v>
       </c>
       <c r="D373" t="n">
         <v>0</v>
